--- a/plate3d/PLATE3D_GGB.xlsx
+++ b/plate3d/PLATE3D_GGB.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2580" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2652" uniqueCount="140">
   <si>
     <t>GOLDEN GATE BRIDGE  ·  1280.16 m main span  ·  mm, Z up</t>
   </si>
@@ -286,19 +286,28 @@
     <t>sc.lg1_1</t>
   </si>
   <si>
-    <t>ONE CABLE PLANE - 128 bars on the parabola, 127 suspenders</t>
+    <t>ONE MAIN CABLE - 130 bars on the parabola, anchorage to anchorage</t>
   </si>
   <si>
     <t>west anchorage. z = ZCL + a x^2 gives every node from here on</t>
   </si>
   <si>
-    <t>md.cbl</t>
+    <t>md.mcb</t>
   </si>
   <si>
-    <t>suspenders - every node but the saddles and the two anchorages</t>
+    <t>THE HANGER ROPES - vertical, one at every node but the saddles</t>
+  </si>
+  <si>
+    <t>the same nodes, straight down to the top chord</t>
+  </si>
+  <si>
+    <t>md.hgr</t>
   </si>
   <si>
     <t>bar.cbl_1</t>
+  </si>
+  <si>
+    <t>bar.hgr_1</t>
   </si>
   <si>
     <t>ONE STIFFENING TRUSS - 25 ft deep, stopping at the tower legs</t>
@@ -322,7 +331,49 @@
     <t>sc.fb_1</t>
   </si>
   <si>
-    <t>one assembly per part - towers, cables, trusses, floor system</t>
+    <t>three drawings, named by the sheet. Save DXF asks for the scale</t>
+  </si>
+  <si>
+    <t># VIEW</t>
+  </si>
+  <si>
+    <t>module</t>
+  </si>
+  <si>
+    <t>dir</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>EL</t>
+  </si>
+  <si>
+    <t>scale</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>VIEW</t>
+  </si>
+  <si>
+    <t>RIGHT</t>
+  </si>
+  <si>
+    <t>TOWER - ELEVATION ACROSS THE BRIDGE</t>
+  </si>
+  <si>
+    <t>FRONT</t>
+  </si>
+  <si>
+    <t>TOWER - ELEVATION ALONG THE BRIDGE</t>
+  </si>
+  <si>
+    <t>STIFFENING TRUSS - GENERAL ARRANGEMENT</t>
+  </si>
+  <si>
+    <t>one assembly per part - towers, main cables, ropes, trusses, deck</t>
   </si>
   <si>
     <t># ASSY</t>
@@ -355,10 +406,16 @@
     <t>ADD</t>
   </si>
   <si>
-    <t>MAIN CABLES AND SUSPENDERS - one plane, both sides</t>
+    <t>MAIN CABLES - one plane, both sides</t>
   </si>
   <si>
-    <t>as.cbl</t>
+    <t>as.mcb</t>
+  </si>
+  <si>
+    <t>HANGER ROPES - the same two planes, hung off the cables above</t>
+  </si>
+  <si>
+    <t>as.hgr</t>
   </si>
   <si>
     <t>STIFFENING TRUSSES - one plane, both sides</t>
@@ -767,7 +824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R396"/>
+  <dimension ref="A1:R408"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
@@ -8703,13 +8760,13 @@
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>3</v>
+        <v>95</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C196" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D196" t="s">
         <v>45</v>
@@ -8753,7 +8810,7 @@
         <v>79</v>
       </c>
       <c r="C197" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D197" t="s">
         <v>45</v>
@@ -8797,7 +8854,7 @@
         <v>79</v>
       </c>
       <c r="C198" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D198" t="s">
         <v>45</v>
@@ -8841,7 +8898,7 @@
         <v>79</v>
       </c>
       <c r="C199" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D199" t="s">
         <v>45</v>
@@ -8885,7 +8942,7 @@
         <v>79</v>
       </c>
       <c r="C200" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D200" t="s">
         <v>45</v>
@@ -8929,7 +8986,7 @@
         <v>79</v>
       </c>
       <c r="C201" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D201" t="s">
         <v>45</v>
@@ -8973,7 +9030,7 @@
         <v>79</v>
       </c>
       <c r="C202" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D202" t="s">
         <v>45</v>
@@ -9017,7 +9074,7 @@
         <v>79</v>
       </c>
       <c r="C203" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D203" t="s">
         <v>45</v>
@@ -9061,7 +9118,7 @@
         <v>79</v>
       </c>
       <c r="C204" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D204" t="s">
         <v>45</v>
@@ -9105,7 +9162,7 @@
         <v>79</v>
       </c>
       <c r="C205" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D205" t="s">
         <v>45</v>
@@ -9149,7 +9206,7 @@
         <v>79</v>
       </c>
       <c r="C206" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D206" t="s">
         <v>45</v>
@@ -9193,7 +9250,7 @@
         <v>79</v>
       </c>
       <c r="C207" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D207" t="s">
         <v>45</v>
@@ -9237,7 +9294,7 @@
         <v>79</v>
       </c>
       <c r="C208" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D208" t="s">
         <v>45</v>
@@ -9281,7 +9338,7 @@
         <v>79</v>
       </c>
       <c r="C209" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D209" t="s">
         <v>45</v>
@@ -9325,7 +9382,7 @@
         <v>79</v>
       </c>
       <c r="C210" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D210" t="s">
         <v>45</v>
@@ -9369,7 +9426,7 @@
         <v>79</v>
       </c>
       <c r="C211" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D211" t="s">
         <v>45</v>
@@ -9413,7 +9470,7 @@
         <v>79</v>
       </c>
       <c r="C212" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D212" t="s">
         <v>45</v>
@@ -9457,7 +9514,7 @@
         <v>79</v>
       </c>
       <c r="C213" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D213" t="s">
         <v>45</v>
@@ -9501,7 +9558,7 @@
         <v>79</v>
       </c>
       <c r="C214" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D214" t="s">
         <v>45</v>
@@ -9545,7 +9602,7 @@
         <v>79</v>
       </c>
       <c r="C215" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D215" t="s">
         <v>45</v>
@@ -9589,7 +9646,7 @@
         <v>79</v>
       </c>
       <c r="C216" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D216" t="s">
         <v>45</v>
@@ -9633,7 +9690,7 @@
         <v>79</v>
       </c>
       <c r="C217" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D217" t="s">
         <v>45</v>
@@ -9677,7 +9734,7 @@
         <v>79</v>
       </c>
       <c r="C218" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D218" t="s">
         <v>45</v>
@@ -9721,7 +9778,7 @@
         <v>79</v>
       </c>
       <c r="C219" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D219" t="s">
         <v>45</v>
@@ -9765,7 +9822,7 @@
         <v>79</v>
       </c>
       <c r="C220" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D220" t="s">
         <v>45</v>
@@ -9809,7 +9866,7 @@
         <v>79</v>
       </c>
       <c r="C221" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D221" t="s">
         <v>45</v>
@@ -9853,7 +9910,7 @@
         <v>79</v>
       </c>
       <c r="C222" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D222" t="s">
         <v>45</v>
@@ -9897,7 +9954,7 @@
         <v>79</v>
       </c>
       <c r="C223" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D223" t="s">
         <v>45</v>
@@ -9941,7 +9998,7 @@
         <v>79</v>
       </c>
       <c r="C224" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D224" t="s">
         <v>45</v>
@@ -9985,7 +10042,7 @@
         <v>79</v>
       </c>
       <c r="C225" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D225" t="s">
         <v>45</v>
@@ -10029,7 +10086,7 @@
         <v>79</v>
       </c>
       <c r="C226" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D226" t="s">
         <v>45</v>
@@ -10073,7 +10130,7 @@
         <v>79</v>
       </c>
       <c r="C227" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D227" t="s">
         <v>45</v>
@@ -10117,7 +10174,7 @@
         <v>79</v>
       </c>
       <c r="C228" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D228" t="s">
         <v>45</v>
@@ -10161,7 +10218,7 @@
         <v>79</v>
       </c>
       <c r="C229" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D229" t="s">
         <v>45</v>
@@ -10205,7 +10262,7 @@
         <v>79</v>
       </c>
       <c r="C230" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D230" t="s">
         <v>45</v>
@@ -10249,7 +10306,7 @@
         <v>79</v>
       </c>
       <c r="C231" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D231" t="s">
         <v>45</v>
@@ -10293,7 +10350,7 @@
         <v>79</v>
       </c>
       <c r="C232" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D232" t="s">
         <v>45</v>
@@ -10337,7 +10394,7 @@
         <v>79</v>
       </c>
       <c r="C233" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D233" t="s">
         <v>45</v>
@@ -10381,7 +10438,7 @@
         <v>79</v>
       </c>
       <c r="C234" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D234" t="s">
         <v>45</v>
@@ -10425,7 +10482,7 @@
         <v>79</v>
       </c>
       <c r="C235" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D235" t="s">
         <v>45</v>
@@ -10469,7 +10526,7 @@
         <v>79</v>
       </c>
       <c r="C236" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D236" t="s">
         <v>45</v>
@@ -10513,7 +10570,7 @@
         <v>79</v>
       </c>
       <c r="C237" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D237" t="s">
         <v>45</v>
@@ -10557,7 +10614,7 @@
         <v>79</v>
       </c>
       <c r="C238" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D238" t="s">
         <v>45</v>
@@ -10601,7 +10658,7 @@
         <v>79</v>
       </c>
       <c r="C239" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D239" t="s">
         <v>45</v>
@@ -10645,7 +10702,7 @@
         <v>79</v>
       </c>
       <c r="C240" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D240" t="s">
         <v>45</v>
@@ -10689,7 +10746,7 @@
         <v>79</v>
       </c>
       <c r="C241" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D241" t="s">
         <v>45</v>
@@ -10733,7 +10790,7 @@
         <v>79</v>
       </c>
       <c r="C242" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D242" t="s">
         <v>45</v>
@@ -10777,7 +10834,7 @@
         <v>79</v>
       </c>
       <c r="C243" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D243" t="s">
         <v>45</v>
@@ -10821,7 +10878,7 @@
         <v>79</v>
       </c>
       <c r="C244" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D244" t="s">
         <v>45</v>
@@ -10865,7 +10922,7 @@
         <v>79</v>
       </c>
       <c r="C245" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D245" t="s">
         <v>45</v>
@@ -10909,7 +10966,7 @@
         <v>79</v>
       </c>
       <c r="C246" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D246" t="s">
         <v>45</v>
@@ -10953,7 +11010,7 @@
         <v>79</v>
       </c>
       <c r="C247" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D247" t="s">
         <v>45</v>
@@ -10997,7 +11054,7 @@
         <v>79</v>
       </c>
       <c r="C248" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D248" t="s">
         <v>45</v>
@@ -11041,7 +11098,7 @@
         <v>79</v>
       </c>
       <c r="C249" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D249" t="s">
         <v>45</v>
@@ -11085,7 +11142,7 @@
         <v>79</v>
       </c>
       <c r="C250" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D250" t="s">
         <v>45</v>
@@ -11129,7 +11186,7 @@
         <v>79</v>
       </c>
       <c r="C251" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D251" t="s">
         <v>45</v>
@@ -11173,7 +11230,7 @@
         <v>79</v>
       </c>
       <c r="C252" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D252" t="s">
         <v>45</v>
@@ -11217,7 +11274,7 @@
         <v>79</v>
       </c>
       <c r="C253" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D253" t="s">
         <v>45</v>
@@ -11261,7 +11318,7 @@
         <v>79</v>
       </c>
       <c r="C254" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D254" t="s">
         <v>45</v>
@@ -11305,7 +11362,7 @@
         <v>79</v>
       </c>
       <c r="C255" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D255" t="s">
         <v>45</v>
@@ -11349,7 +11406,7 @@
         <v>79</v>
       </c>
       <c r="C256" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D256" t="s">
         <v>45</v>
@@ -11393,7 +11450,7 @@
         <v>79</v>
       </c>
       <c r="C257" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D257" t="s">
         <v>45</v>
@@ -11437,7 +11494,7 @@
         <v>79</v>
       </c>
       <c r="C258" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D258" t="s">
         <v>45</v>
@@ -11481,7 +11538,7 @@
         <v>79</v>
       </c>
       <c r="C259" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D259" t="s">
         <v>45</v>
@@ -11525,7 +11582,7 @@
         <v>79</v>
       </c>
       <c r="C260" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D260" t="s">
         <v>45</v>
@@ -11569,7 +11626,7 @@
         <v>79</v>
       </c>
       <c r="C261" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D261" t="s">
         <v>45</v>
@@ -11613,7 +11670,7 @@
         <v>79</v>
       </c>
       <c r="C262" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D262" t="s">
         <v>45</v>
@@ -11657,7 +11714,7 @@
         <v>79</v>
       </c>
       <c r="C263" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D263" t="s">
         <v>45</v>
@@ -11701,7 +11758,7 @@
         <v>79</v>
       </c>
       <c r="C264" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D264" t="s">
         <v>45</v>
@@ -11745,7 +11802,7 @@
         <v>79</v>
       </c>
       <c r="C265" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D265" t="s">
         <v>45</v>
@@ -11789,7 +11846,7 @@
         <v>79</v>
       </c>
       <c r="C266" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D266" t="s">
         <v>45</v>
@@ -11833,7 +11890,7 @@
         <v>79</v>
       </c>
       <c r="C267" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D267" t="s">
         <v>45</v>
@@ -11877,7 +11934,7 @@
         <v>79</v>
       </c>
       <c r="C268" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D268" t="s">
         <v>45</v>
@@ -11921,7 +11978,7 @@
         <v>79</v>
       </c>
       <c r="C269" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D269" t="s">
         <v>45</v>
@@ -11965,7 +12022,7 @@
         <v>79</v>
       </c>
       <c r="C270" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D270" t="s">
         <v>45</v>
@@ -12009,7 +12066,7 @@
         <v>79</v>
       </c>
       <c r="C271" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D271" t="s">
         <v>45</v>
@@ -12053,7 +12110,7 @@
         <v>79</v>
       </c>
       <c r="C272" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D272" t="s">
         <v>45</v>
@@ -12097,7 +12154,7 @@
         <v>79</v>
       </c>
       <c r="C273" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D273" t="s">
         <v>45</v>
@@ -12141,7 +12198,7 @@
         <v>79</v>
       </c>
       <c r="C274" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D274" t="s">
         <v>45</v>
@@ -12185,7 +12242,7 @@
         <v>79</v>
       </c>
       <c r="C275" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D275" t="s">
         <v>45</v>
@@ -12229,7 +12286,7 @@
         <v>79</v>
       </c>
       <c r="C276" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D276" t="s">
         <v>45</v>
@@ -12273,7 +12330,7 @@
         <v>79</v>
       </c>
       <c r="C277" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D277" t="s">
         <v>45</v>
@@ -12317,7 +12374,7 @@
         <v>79</v>
       </c>
       <c r="C278" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D278" t="s">
         <v>45</v>
@@ -12361,7 +12418,7 @@
         <v>79</v>
       </c>
       <c r="C279" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D279" t="s">
         <v>45</v>
@@ -12405,7 +12462,7 @@
         <v>79</v>
       </c>
       <c r="C280" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D280" t="s">
         <v>45</v>
@@ -12449,7 +12506,7 @@
         <v>79</v>
       </c>
       <c r="C281" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D281" t="s">
         <v>45</v>
@@ -12493,7 +12550,7 @@
         <v>79</v>
       </c>
       <c r="C282" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D282" t="s">
         <v>45</v>
@@ -12537,7 +12594,7 @@
         <v>79</v>
       </c>
       <c r="C283" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D283" t="s">
         <v>45</v>
@@ -12581,7 +12638,7 @@
         <v>79</v>
       </c>
       <c r="C284" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D284" t="s">
         <v>45</v>
@@ -12625,7 +12682,7 @@
         <v>79</v>
       </c>
       <c r="C285" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D285" t="s">
         <v>45</v>
@@ -12669,7 +12726,7 @@
         <v>79</v>
       </c>
       <c r="C286" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D286" t="s">
         <v>45</v>
@@ -12713,7 +12770,7 @@
         <v>79</v>
       </c>
       <c r="C287" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D287" t="s">
         <v>45</v>
@@ -12757,7 +12814,7 @@
         <v>79</v>
       </c>
       <c r="C288" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D288" t="s">
         <v>45</v>
@@ -12801,7 +12858,7 @@
         <v>79</v>
       </c>
       <c r="C289" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D289" t="s">
         <v>45</v>
@@ -12845,7 +12902,7 @@
         <v>79</v>
       </c>
       <c r="C290" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D290" t="s">
         <v>45</v>
@@ -12889,7 +12946,7 @@
         <v>79</v>
       </c>
       <c r="C291" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D291" t="s">
         <v>45</v>
@@ -12933,7 +12990,7 @@
         <v>79</v>
       </c>
       <c r="C292" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D292" t="s">
         <v>45</v>
@@ -12977,7 +13034,7 @@
         <v>79</v>
       </c>
       <c r="C293" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D293" t="s">
         <v>45</v>
@@ -13021,7 +13078,7 @@
         <v>79</v>
       </c>
       <c r="C294" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D294" t="s">
         <v>45</v>
@@ -13065,7 +13122,7 @@
         <v>79</v>
       </c>
       <c r="C295" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D295" t="s">
         <v>45</v>
@@ -13109,7 +13166,7 @@
         <v>79</v>
       </c>
       <c r="C296" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D296" t="s">
         <v>45</v>
@@ -13153,7 +13210,7 @@
         <v>79</v>
       </c>
       <c r="C297" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D297" t="s">
         <v>45</v>
@@ -13197,7 +13254,7 @@
         <v>79</v>
       </c>
       <c r="C298" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D298" t="s">
         <v>45</v>
@@ -13241,7 +13298,7 @@
         <v>79</v>
       </c>
       <c r="C299" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D299" t="s">
         <v>45</v>
@@ -13285,7 +13342,7 @@
         <v>79</v>
       </c>
       <c r="C300" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D300" t="s">
         <v>45</v>
@@ -13329,7 +13386,7 @@
         <v>79</v>
       </c>
       <c r="C301" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D301" t="s">
         <v>45</v>
@@ -13373,7 +13430,7 @@
         <v>79</v>
       </c>
       <c r="C302" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D302" t="s">
         <v>45</v>
@@ -13417,7 +13474,7 @@
         <v>79</v>
       </c>
       <c r="C303" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D303" t="s">
         <v>45</v>
@@ -13461,7 +13518,7 @@
         <v>79</v>
       </c>
       <c r="C304" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D304" t="s">
         <v>45</v>
@@ -13505,7 +13562,7 @@
         <v>79</v>
       </c>
       <c r="C305" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D305" t="s">
         <v>45</v>
@@ -13549,7 +13606,7 @@
         <v>79</v>
       </c>
       <c r="C306" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D306" t="s">
         <v>45</v>
@@ -13593,7 +13650,7 @@
         <v>79</v>
       </c>
       <c r="C307" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D307" t="s">
         <v>45</v>
@@ -13637,7 +13694,7 @@
         <v>79</v>
       </c>
       <c r="C308" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D308" t="s">
         <v>45</v>
@@ -13681,7 +13738,7 @@
         <v>79</v>
       </c>
       <c r="C309" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D309" t="s">
         <v>45</v>
@@ -13725,7 +13782,7 @@
         <v>79</v>
       </c>
       <c r="C310" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D310" t="s">
         <v>45</v>
@@ -13769,7 +13826,7 @@
         <v>79</v>
       </c>
       <c r="C311" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D311" t="s">
         <v>45</v>
@@ -13813,7 +13870,7 @@
         <v>79</v>
       </c>
       <c r="C312" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D312" t="s">
         <v>45</v>
@@ -13857,7 +13914,7 @@
         <v>79</v>
       </c>
       <c r="C313" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D313" t="s">
         <v>45</v>
@@ -13901,7 +13958,7 @@
         <v>79</v>
       </c>
       <c r="C314" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D314" t="s">
         <v>45</v>
@@ -13945,7 +14002,7 @@
         <v>79</v>
       </c>
       <c r="C315" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D315" t="s">
         <v>45</v>
@@ -13989,7 +14046,7 @@
         <v>79</v>
       </c>
       <c r="C316" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D316" t="s">
         <v>45</v>
@@ -14033,7 +14090,7 @@
         <v>79</v>
       </c>
       <c r="C317" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D317" t="s">
         <v>45</v>
@@ -14077,7 +14134,7 @@
         <v>79</v>
       </c>
       <c r="C318" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D318" t="s">
         <v>45</v>
@@ -14121,7 +14178,7 @@
         <v>79</v>
       </c>
       <c r="C319" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D319" t="s">
         <v>45</v>
@@ -14165,7 +14222,7 @@
         <v>79</v>
       </c>
       <c r="C320" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D320" t="s">
         <v>45</v>
@@ -14209,7 +14266,7 @@
         <v>79</v>
       </c>
       <c r="C321" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D321" t="s">
         <v>45</v>
@@ -14253,7 +14310,7 @@
         <v>79</v>
       </c>
       <c r="C322" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D322" t="s">
         <v>45</v>
@@ -14353,192 +14410,150 @@
         <v>89</v>
       </c>
       <c r="E324" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F324" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A325" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B325" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C325" t="s">
+        <v>5</v>
+      </c>
+      <c r="D325" t="s">
+        <v>63</v>
+      </c>
+      <c r="E325" t="s">
+        <v>64</v>
+      </c>
+      <c r="F325" t="s">
+        <v>81</v>
+      </c>
+      <c r="G325" t="s">
+        <v>82</v>
+      </c>
+      <c r="H325" t="s">
+        <v>83</v>
+      </c>
+      <c r="I325" t="s">
+        <v>84</v>
+      </c>
+      <c r="J325" t="s">
+        <v>85</v>
+      </c>
+      <c r="K325" t="s">
+        <v>86</v>
+      </c>
+      <c r="L325" t="s">
+        <v>87</v>
+      </c>
+      <c r="M325" t="s">
+        <v>74</v>
+      </c>
+      <c r="N325" t="s">
+        <v>75</v>
+      </c>
+      <c r="O325" t="s">
+        <v>76</v>
+      </c>
+      <c r="P325" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B326" s="3" t="s">
-        <v>60</v>
+      <c r="B326" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="C326" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A327" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B327" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C327" t="s">
-        <v>5</v>
-      </c>
-      <c r="D327" t="s">
-        <v>63</v>
-      </c>
-      <c r="E327" t="s">
-        <v>64</v>
-      </c>
-      <c r="F327" t="s">
-        <v>65</v>
-      </c>
-      <c r="G327" t="s">
-        <v>66</v>
-      </c>
-      <c r="H327" t="s">
-        <v>67</v>
-      </c>
-      <c r="I327" t="s">
-        <v>68</v>
-      </c>
-      <c r="J327" t="s">
-        <v>69</v>
-      </c>
-      <c r="K327" t="s">
-        <v>70</v>
-      </c>
-      <c r="L327" t="s">
-        <v>71</v>
-      </c>
-      <c r="M327" t="s">
-        <v>72</v>
-      </c>
-      <c r="N327" t="s">
-        <v>73</v>
-      </c>
-      <c r="O327" t="s">
-        <v>74</v>
-      </c>
-      <c r="P327" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q327" t="s">
-        <v>76</v>
-      </c>
-      <c r="R327" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="D326" t="s">
+        <v>89</v>
+      </c>
+      <c r="E326" t="s">
+        <v>98</v>
+      </c>
+      <c r="F326" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B328" s="2" t="s">
-        <v>79</v>
+      <c r="B328" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="C328" t="s">
-        <v>98</v>
-      </c>
-      <c r="D328" t="s">
-        <v>33</v>
-      </c>
-      <c r="E328" t="s">
-        <v>3</v>
-      </c>
-      <c r="F328">
-        <v>-982980</v>
-      </c>
-      <c r="G328">
-        <v>0</v>
-      </c>
-      <c r="H328">
-        <v>74076</v>
-      </c>
-      <c r="I328">
-        <v>-967393.6</v>
-      </c>
-      <c r="J328">
-        <v>0</v>
-      </c>
-      <c r="K328">
-        <v>74076</v>
-      </c>
-      <c r="L328" t="s">
-        <v>3</v>
-      </c>
-      <c r="M328" t="s">
-        <v>3</v>
-      </c>
-      <c r="N328" t="s">
-        <v>3</v>
-      </c>
-      <c r="O328">
-        <v>15586.4</v>
-      </c>
-      <c r="P328">
-        <v>0</v>
-      </c>
-      <c r="Q328">
-        <v>0</v>
-      </c>
-      <c r="R328">
-        <v>20</v>
+        <v>99</v>
       </c>
     </row>
     <row r="329" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B329" s="2" t="s">
-        <v>79</v>
+        <v>100</v>
+      </c>
+      <c r="B329" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C329" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
       <c r="D329" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="E329" t="s">
-        <v>3</v>
-      </c>
-      <c r="F329">
-        <v>-982980</v>
-      </c>
-      <c r="G329">
-        <v>0</v>
-      </c>
-      <c r="H329">
-        <v>67656</v>
-      </c>
-      <c r="I329">
-        <v>-967393.6</v>
-      </c>
-      <c r="J329">
-        <v>0</v>
-      </c>
-      <c r="K329">
-        <v>67656</v>
+        <v>64</v>
+      </c>
+      <c r="F329" t="s">
+        <v>65</v>
+      </c>
+      <c r="G329" t="s">
+        <v>66</v>
+      </c>
+      <c r="H329" t="s">
+        <v>67</v>
+      </c>
+      <c r="I329" t="s">
+        <v>68</v>
+      </c>
+      <c r="J329" t="s">
+        <v>69</v>
+      </c>
+      <c r="K329" t="s">
+        <v>70</v>
       </c>
       <c r="L329" t="s">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="M329" t="s">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="N329" t="s">
-        <v>3</v>
-      </c>
-      <c r="O329">
-        <v>15586.4</v>
-      </c>
-      <c r="P329">
-        <v>0</v>
-      </c>
-      <c r="Q329">
-        <v>0</v>
-      </c>
-      <c r="R329">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="O329" t="s">
+        <v>74</v>
+      </c>
+      <c r="P329" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q329" t="s">
+        <v>76</v>
+      </c>
+      <c r="R329" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="330" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>3</v>
       </c>
@@ -14546,7 +14561,7 @@
         <v>79</v>
       </c>
       <c r="C330" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D330" t="s">
         <v>33</v>
@@ -14555,7 +14570,7 @@
         <v>3</v>
       </c>
       <c r="F330">
-        <v>-655666.4</v>
+        <v>-982980</v>
       </c>
       <c r="G330">
         <v>0</v>
@@ -14564,7 +14579,7 @@
         <v>74076</v>
       </c>
       <c r="I330">
-        <v>-647823.7</v>
+        <v>-967393.6</v>
       </c>
       <c r="J330">
         <v>0</v>
@@ -14572,8 +14587,8 @@
       <c r="K330">
         <v>74076</v>
       </c>
-      <c r="L330">
-        <v>10</v>
+      <c r="L330" t="s">
+        <v>3</v>
       </c>
       <c r="M330" t="s">
         <v>3</v>
@@ -14581,8 +14596,20 @@
       <c r="N330" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O330">
+        <v>15586.4</v>
+      </c>
+      <c r="P330">
+        <v>0</v>
+      </c>
+      <c r="Q330">
+        <v>0</v>
+      </c>
+      <c r="R330">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="331" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>3</v>
       </c>
@@ -14590,7 +14617,7 @@
         <v>79</v>
       </c>
       <c r="C331" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D331" t="s">
         <v>33</v>
@@ -14599,7 +14626,7 @@
         <v>3</v>
       </c>
       <c r="F331">
-        <v>-655666.4</v>
+        <v>-982980</v>
       </c>
       <c r="G331">
         <v>0</v>
@@ -14608,7 +14635,7 @@
         <v>67656</v>
       </c>
       <c r="I331">
-        <v>-647823.7</v>
+        <v>-967393.6</v>
       </c>
       <c r="J331">
         <v>0</v>
@@ -14616,73 +14643,73 @@
       <c r="K331">
         <v>67656</v>
       </c>
-      <c r="L331">
+      <c r="L331" t="s">
+        <v>3</v>
+      </c>
+      <c r="M331" t="s">
+        <v>3</v>
+      </c>
+      <c r="N331" t="s">
+        <v>3</v>
+      </c>
+      <c r="O331">
+        <v>15586.4</v>
+      </c>
+      <c r="P331">
+        <v>0</v>
+      </c>
+      <c r="Q331">
+        <v>0</v>
+      </c>
+      <c r="R331">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="332" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A332" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C332" t="s">
+        <v>101</v>
+      </c>
+      <c r="D332" t="s">
+        <v>33</v>
+      </c>
+      <c r="E332" t="s">
+        <v>3</v>
+      </c>
+      <c r="F332">
+        <v>-655666.4</v>
+      </c>
+      <c r="G332">
+        <v>0</v>
+      </c>
+      <c r="H332">
+        <v>74076</v>
+      </c>
+      <c r="I332">
+        <v>-647823.7</v>
+      </c>
+      <c r="J332">
+        <v>0</v>
+      </c>
+      <c r="K332">
+        <v>74076</v>
+      </c>
+      <c r="L332">
         <v>10</v>
       </c>
-      <c r="M331" t="s">
-        <v>3</v>
-      </c>
-      <c r="N331" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="332" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A332" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B332" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C332" t="s">
-        <v>98</v>
-      </c>
-      <c r="D332" t="s">
-        <v>35</v>
-      </c>
-      <c r="E332" t="s">
-        <v>3</v>
-      </c>
-      <c r="F332">
-        <v>-982980</v>
-      </c>
-      <c r="G332">
-        <v>0</v>
-      </c>
-      <c r="H332">
-        <v>68266</v>
-      </c>
-      <c r="I332">
-        <v>-982980</v>
-      </c>
-      <c r="J332">
-        <v>0</v>
-      </c>
-      <c r="K332">
-        <v>73466</v>
-      </c>
-      <c r="L332" t="s">
-        <v>3</v>
-      </c>
       <c r="M332" t="s">
         <v>3</v>
       </c>
       <c r="N332" t="s">
         <v>3</v>
       </c>
-      <c r="O332">
-        <v>15586.4</v>
-      </c>
-      <c r="P332">
-        <v>0</v>
-      </c>
-      <c r="Q332">
-        <v>0</v>
-      </c>
-      <c r="R332">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="333" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="333" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>3</v>
       </c>
@@ -14690,52 +14717,40 @@
         <v>79</v>
       </c>
       <c r="C333" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D333" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E333" t="s">
         <v>3</v>
       </c>
       <c r="F333">
-        <v>-982380</v>
+        <v>-655666.4</v>
       </c>
       <c r="G333">
         <v>0</v>
       </c>
       <c r="H333">
-        <v>68656</v>
+        <v>67656</v>
       </c>
       <c r="I333">
-        <v>-967993.6</v>
+        <v>-647823.7</v>
       </c>
       <c r="J333">
         <v>0</v>
       </c>
       <c r="K333">
-        <v>73076</v>
-      </c>
-      <c r="L333" t="s">
-        <v>3</v>
+        <v>67656</v>
+      </c>
+      <c r="L333">
+        <v>10</v>
       </c>
       <c r="M333" t="s">
         <v>3</v>
       </c>
       <c r="N333" t="s">
         <v>3</v>
-      </c>
-      <c r="O333">
-        <v>15586.4</v>
-      </c>
-      <c r="P333">
-        <v>0</v>
-      </c>
-      <c r="Q333">
-        <v>0</v>
-      </c>
-      <c r="R333">
-        <v>20</v>
       </c>
     </row>
     <row r="334" spans="1:18" x14ac:dyDescent="0.25">
@@ -14746,31 +14761,31 @@
         <v>79</v>
       </c>
       <c r="C334" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D334" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E334" t="s">
         <v>3</v>
       </c>
       <c r="F334">
-        <v>-624840</v>
+        <v>-982980</v>
       </c>
       <c r="G334">
         <v>0</v>
       </c>
       <c r="H334">
-        <v>74076</v>
+        <v>68266</v>
       </c>
       <c r="I334">
-        <v>-609600</v>
+        <v>-982980</v>
       </c>
       <c r="J334">
         <v>0</v>
       </c>
       <c r="K334">
-        <v>74076</v>
+        <v>73466</v>
       </c>
       <c r="L334" t="s">
         <v>3</v>
@@ -14782,7 +14797,7 @@
         <v>3</v>
       </c>
       <c r="O334">
-        <v>15240</v>
+        <v>15586.4</v>
       </c>
       <c r="P334">
         <v>0</v>
@@ -14791,7 +14806,7 @@
         <v>0</v>
       </c>
       <c r="R334">
-        <v>81</v>
+        <v>21</v>
       </c>
     </row>
     <row r="335" spans="1:18" x14ac:dyDescent="0.25">
@@ -14802,31 +14817,31 @@
         <v>79</v>
       </c>
       <c r="C335" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D335" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E335" t="s">
         <v>3</v>
       </c>
       <c r="F335">
-        <v>-624840</v>
+        <v>-982380</v>
       </c>
       <c r="G335">
         <v>0</v>
       </c>
       <c r="H335">
-        <v>67656</v>
+        <v>68656</v>
       </c>
       <c r="I335">
-        <v>-609600</v>
+        <v>-967993.6</v>
       </c>
       <c r="J335">
         <v>0</v>
       </c>
       <c r="K335">
-        <v>67656</v>
+        <v>73076</v>
       </c>
       <c r="L335" t="s">
         <v>3</v>
@@ -14838,7 +14853,7 @@
         <v>3</v>
       </c>
       <c r="O335">
-        <v>15240</v>
+        <v>15586.4</v>
       </c>
       <c r="P335">
         <v>0</v>
@@ -14847,10 +14862,10 @@
         <v>0</v>
       </c>
       <c r="R335">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="336" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>3</v>
       </c>
@@ -14858,7 +14873,7 @@
         <v>79</v>
       </c>
       <c r="C336" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D336" t="s">
         <v>33</v>
@@ -14867,7 +14882,7 @@
         <v>3</v>
       </c>
       <c r="F336">
-        <v>-632336.3</v>
+        <v>-624840</v>
       </c>
       <c r="G336">
         <v>0</v>
@@ -14876,7 +14891,7 @@
         <v>74076</v>
       </c>
       <c r="I336">
-        <v>-624840</v>
+        <v>-609600</v>
       </c>
       <c r="J336">
         <v>0</v>
@@ -14887,14 +14902,26 @@
       <c r="L336" t="s">
         <v>3</v>
       </c>
-      <c r="M336">
-        <v>10</v>
+      <c r="M336" t="s">
+        <v>3</v>
       </c>
       <c r="N336" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O336">
+        <v>15240</v>
+      </c>
+      <c r="P336">
+        <v>0</v>
+      </c>
+      <c r="Q336">
+        <v>0</v>
+      </c>
+      <c r="R336">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="337" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>3</v>
       </c>
@@ -14902,7 +14929,7 @@
         <v>79</v>
       </c>
       <c r="C337" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D337" t="s">
         <v>33</v>
@@ -14911,7 +14938,7 @@
         <v>3</v>
       </c>
       <c r="F337">
-        <v>-632336.3</v>
+        <v>-624840</v>
       </c>
       <c r="G337">
         <v>0</v>
@@ -14920,7 +14947,7 @@
         <v>67656</v>
       </c>
       <c r="I337">
-        <v>-624840</v>
+        <v>-609600</v>
       </c>
       <c r="J337">
         <v>0</v>
@@ -14931,11 +14958,23 @@
       <c r="L337" t="s">
         <v>3</v>
       </c>
-      <c r="M337">
-        <v>10</v>
+      <c r="M337" t="s">
+        <v>3</v>
       </c>
       <c r="N337" t="s">
         <v>3</v>
+      </c>
+      <c r="O337">
+        <v>15240</v>
+      </c>
+      <c r="P337">
+        <v>0</v>
+      </c>
+      <c r="Q337">
+        <v>0</v>
+      </c>
+      <c r="R337">
+        <v>81</v>
       </c>
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.25">
@@ -14946,7 +14985,7 @@
         <v>79</v>
       </c>
       <c r="C338" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D338" t="s">
         <v>33</v>
@@ -14955,7 +14994,7 @@
         <v>3</v>
       </c>
       <c r="F338">
-        <v>624840</v>
+        <v>-632336.3</v>
       </c>
       <c r="G338">
         <v>0</v>
@@ -14964,7 +15003,7 @@
         <v>74076</v>
       </c>
       <c r="I338">
-        <v>632336.3</v>
+        <v>-624840</v>
       </c>
       <c r="J338">
         <v>0</v>
@@ -14972,11 +15011,11 @@
       <c r="K338">
         <v>74076</v>
       </c>
-      <c r="L338">
+      <c r="L338" t="s">
+        <v>3</v>
+      </c>
+      <c r="M338">
         <v>10</v>
-      </c>
-      <c r="M338" t="s">
-        <v>3</v>
       </c>
       <c r="N338" t="s">
         <v>3</v>
@@ -14990,7 +15029,7 @@
         <v>79</v>
       </c>
       <c r="C339" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D339" t="s">
         <v>33</v>
@@ -14999,7 +15038,7 @@
         <v>3</v>
       </c>
       <c r="F339">
-        <v>624840</v>
+        <v>-632336.3</v>
       </c>
       <c r="G339">
         <v>0</v>
@@ -15008,7 +15047,7 @@
         <v>67656</v>
       </c>
       <c r="I339">
-        <v>632336.3</v>
+        <v>-624840</v>
       </c>
       <c r="J339">
         <v>0</v>
@@ -15016,17 +15055,17 @@
       <c r="K339">
         <v>67656</v>
       </c>
-      <c r="L339">
+      <c r="L339" t="s">
+        <v>3</v>
+      </c>
+      <c r="M339">
         <v>10</v>
       </c>
-      <c r="M339" t="s">
-        <v>3</v>
-      </c>
       <c r="N339" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="340" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>3</v>
       </c>
@@ -15034,34 +15073,34 @@
         <v>79</v>
       </c>
       <c r="C340" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D340" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E340" t="s">
         <v>3</v>
       </c>
       <c r="F340">
-        <v>-624840</v>
+        <v>624840</v>
       </c>
       <c r="G340">
         <v>0</v>
       </c>
       <c r="H340">
-        <v>68266</v>
+        <v>74076</v>
       </c>
       <c r="I340">
-        <v>-624840</v>
+        <v>632336.3</v>
       </c>
       <c r="J340">
         <v>0</v>
       </c>
       <c r="K340">
-        <v>73466</v>
-      </c>
-      <c r="L340" t="s">
-        <v>3</v>
+        <v>74076</v>
+      </c>
+      <c r="L340">
+        <v>10</v>
       </c>
       <c r="M340" t="s">
         <v>3</v>
@@ -15069,20 +15108,8 @@
       <c r="N340" t="s">
         <v>3</v>
       </c>
-      <c r="O340">
-        <v>15240</v>
-      </c>
-      <c r="P340">
-        <v>0</v>
-      </c>
-      <c r="Q340">
-        <v>0</v>
-      </c>
-      <c r="R340">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="341" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="341" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>3</v>
       </c>
@@ -15090,52 +15117,40 @@
         <v>79</v>
       </c>
       <c r="C341" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D341" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E341" t="s">
         <v>3</v>
       </c>
       <c r="F341">
-        <v>-624240</v>
+        <v>624840</v>
       </c>
       <c r="G341">
         <v>0</v>
       </c>
       <c r="H341">
-        <v>68656</v>
+        <v>67656</v>
       </c>
       <c r="I341">
-        <v>-610200</v>
+        <v>632336.3</v>
       </c>
       <c r="J341">
         <v>0</v>
       </c>
       <c r="K341">
-        <v>73076</v>
-      </c>
-      <c r="L341" t="s">
-        <v>3</v>
+        <v>67656</v>
+      </c>
+      <c r="L341">
+        <v>10</v>
       </c>
       <c r="M341" t="s">
         <v>3</v>
       </c>
       <c r="N341" t="s">
         <v>3</v>
-      </c>
-      <c r="O341">
-        <v>15240</v>
-      </c>
-      <c r="P341">
-        <v>0</v>
-      </c>
-      <c r="Q341">
-        <v>0</v>
-      </c>
-      <c r="R341">
-        <v>40</v>
       </c>
     </row>
     <row r="342" spans="1:18" x14ac:dyDescent="0.25">
@@ -15146,31 +15161,31 @@
         <v>79</v>
       </c>
       <c r="C342" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D342" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E342" t="s">
         <v>3</v>
       </c>
       <c r="F342">
-        <v>600</v>
+        <v>-624840</v>
       </c>
       <c r="G342">
         <v>0</v>
       </c>
       <c r="H342">
-        <v>73076</v>
+        <v>68266</v>
       </c>
       <c r="I342">
-        <v>14640</v>
+        <v>-624840</v>
       </c>
       <c r="J342">
         <v>0</v>
       </c>
       <c r="K342">
-        <v>68656</v>
+        <v>73466</v>
       </c>
       <c r="L342" t="s">
         <v>3</v>
@@ -15191,7 +15206,7 @@
         <v>0</v>
       </c>
       <c r="R342">
-        <v>40</v>
+        <v>82</v>
       </c>
     </row>
     <row r="343" spans="1:18" x14ac:dyDescent="0.25">
@@ -15202,31 +15217,31 @@
         <v>79</v>
       </c>
       <c r="C343" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D343" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E343" t="s">
         <v>3</v>
       </c>
       <c r="F343">
-        <v>655666.4</v>
+        <v>-624240</v>
       </c>
       <c r="G343">
         <v>0</v>
       </c>
       <c r="H343">
-        <v>74076</v>
+        <v>68656</v>
       </c>
       <c r="I343">
-        <v>671252.7</v>
+        <v>-610200</v>
       </c>
       <c r="J343">
         <v>0</v>
       </c>
       <c r="K343">
-        <v>74076</v>
+        <v>73076</v>
       </c>
       <c r="L343" t="s">
         <v>3</v>
@@ -15238,7 +15253,7 @@
         <v>3</v>
       </c>
       <c r="O343">
-        <v>15586.4</v>
+        <v>15240</v>
       </c>
       <c r="P343">
         <v>0</v>
@@ -15247,7 +15262,7 @@
         <v>0</v>
       </c>
       <c r="R343">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="344" spans="1:18" x14ac:dyDescent="0.25">
@@ -15258,31 +15273,31 @@
         <v>79</v>
       </c>
       <c r="C344" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D344" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E344" t="s">
         <v>3</v>
       </c>
       <c r="F344">
-        <v>655666.4</v>
+        <v>600</v>
       </c>
       <c r="G344">
         <v>0</v>
       </c>
       <c r="H344">
-        <v>67656</v>
+        <v>73076</v>
       </c>
       <c r="I344">
-        <v>671252.7</v>
+        <v>14640</v>
       </c>
       <c r="J344">
         <v>0</v>
       </c>
       <c r="K344">
-        <v>67656</v>
+        <v>68656</v>
       </c>
       <c r="L344" t="s">
         <v>3</v>
@@ -15294,7 +15309,7 @@
         <v>3</v>
       </c>
       <c r="O344">
-        <v>15586.4</v>
+        <v>15240</v>
       </c>
       <c r="P344">
         <v>0</v>
@@ -15303,10 +15318,10 @@
         <v>0</v>
       </c>
       <c r="R344">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="345" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>3</v>
       </c>
@@ -15314,7 +15329,7 @@
         <v>79</v>
       </c>
       <c r="C345" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D345" t="s">
         <v>33</v>
@@ -15323,7 +15338,7 @@
         <v>3</v>
       </c>
       <c r="F345">
-        <v>647823.7</v>
+        <v>655666.4</v>
       </c>
       <c r="G345">
         <v>0</v>
@@ -15332,7 +15347,7 @@
         <v>74076</v>
       </c>
       <c r="I345">
-        <v>655666.4</v>
+        <v>671252.7</v>
       </c>
       <c r="J345">
         <v>0</v>
@@ -15343,14 +15358,26 @@
       <c r="L345" t="s">
         <v>3</v>
       </c>
-      <c r="M345">
-        <v>10</v>
+      <c r="M345" t="s">
+        <v>3</v>
       </c>
       <c r="N345" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O345">
+        <v>15586.4</v>
+      </c>
+      <c r="P345">
+        <v>0</v>
+      </c>
+      <c r="Q345">
+        <v>0</v>
+      </c>
+      <c r="R345">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="346" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>3</v>
       </c>
@@ -15358,7 +15385,7 @@
         <v>79</v>
       </c>
       <c r="C346" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D346" t="s">
         <v>33</v>
@@ -15367,7 +15394,7 @@
         <v>3</v>
       </c>
       <c r="F346">
-        <v>647823.7</v>
+        <v>655666.4</v>
       </c>
       <c r="G346">
         <v>0</v>
@@ -15376,7 +15403,7 @@
         <v>67656</v>
       </c>
       <c r="I346">
-        <v>655666.4</v>
+        <v>671252.7</v>
       </c>
       <c r="J346">
         <v>0</v>
@@ -15387,14 +15414,26 @@
       <c r="L346" t="s">
         <v>3</v>
       </c>
-      <c r="M346">
-        <v>10</v>
+      <c r="M346" t="s">
+        <v>3</v>
       </c>
       <c r="N346" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="347" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O346">
+        <v>15586.4</v>
+      </c>
+      <c r="P346">
+        <v>0</v>
+      </c>
+      <c r="Q346">
+        <v>0</v>
+      </c>
+      <c r="R346">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="347" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>3</v>
       </c>
@@ -15402,22 +15441,22 @@
         <v>79</v>
       </c>
       <c r="C347" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D347" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E347" t="s">
         <v>3</v>
       </c>
       <c r="F347">
-        <v>655666.4</v>
+        <v>647823.7</v>
       </c>
       <c r="G347">
         <v>0</v>
       </c>
       <c r="H347">
-        <v>68266</v>
+        <v>74076</v>
       </c>
       <c r="I347">
         <v>655666.4</v>
@@ -15426,333 +15465,309 @@
         <v>0</v>
       </c>
       <c r="K347">
+        <v>74076</v>
+      </c>
+      <c r="L347" t="s">
+        <v>3</v>
+      </c>
+      <c r="M347">
+        <v>10</v>
+      </c>
+      <c r="N347" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="348" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A348" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C348" t="s">
+        <v>101</v>
+      </c>
+      <c r="D348" t="s">
+        <v>33</v>
+      </c>
+      <c r="E348" t="s">
+        <v>3</v>
+      </c>
+      <c r="F348">
+        <v>647823.7</v>
+      </c>
+      <c r="G348">
+        <v>0</v>
+      </c>
+      <c r="H348">
+        <v>67656</v>
+      </c>
+      <c r="I348">
+        <v>655666.4</v>
+      </c>
+      <c r="J348">
+        <v>0</v>
+      </c>
+      <c r="K348">
+        <v>67656</v>
+      </c>
+      <c r="L348" t="s">
+        <v>3</v>
+      </c>
+      <c r="M348">
+        <v>10</v>
+      </c>
+      <c r="N348" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="349" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A349" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B349" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C349" t="s">
+        <v>101</v>
+      </c>
+      <c r="D349" t="s">
+        <v>35</v>
+      </c>
+      <c r="E349" t="s">
+        <v>3</v>
+      </c>
+      <c r="F349">
+        <v>655666.4</v>
+      </c>
+      <c r="G349">
+        <v>0</v>
+      </c>
+      <c r="H349">
+        <v>68266</v>
+      </c>
+      <c r="I349">
+        <v>655666.4</v>
+      </c>
+      <c r="J349">
+        <v>0</v>
+      </c>
+      <c r="K349">
         <v>73466</v>
       </c>
-      <c r="L347" t="s">
-        <v>3</v>
-      </c>
-      <c r="M347" t="s">
-        <v>3</v>
-      </c>
-      <c r="N347" t="s">
-        <v>3</v>
-      </c>
-      <c r="O347">
+      <c r="L349" t="s">
+        <v>3</v>
+      </c>
+      <c r="M349" t="s">
+        <v>3</v>
+      </c>
+      <c r="N349" t="s">
+        <v>3</v>
+      </c>
+      <c r="O349">
         <v>15586.4</v>
       </c>
-      <c r="P347">
-        <v>0</v>
-      </c>
-      <c r="Q347">
-        <v>0</v>
-      </c>
-      <c r="R347">
+      <c r="P349">
+        <v>0</v>
+      </c>
+      <c r="Q349">
+        <v>0</v>
+      </c>
+      <c r="R349">
         <v>21</v>
       </c>
     </row>
-    <row r="348" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A348" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B348" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C348" t="s">
-        <v>98</v>
-      </c>
-      <c r="D348" t="s">
+    <row r="350" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A350" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B350" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C350" t="s">
+        <v>101</v>
+      </c>
+      <c r="D350" t="s">
         <v>36</v>
       </c>
-      <c r="E348" t="s">
-        <v>3</v>
-      </c>
-      <c r="F348">
+      <c r="E350" t="s">
+        <v>3</v>
+      </c>
+      <c r="F350">
         <v>656266.4</v>
       </c>
-      <c r="G348">
-        <v>0</v>
-      </c>
-      <c r="H348">
+      <c r="G350">
+        <v>0</v>
+      </c>
+      <c r="H350">
         <v>68656</v>
       </c>
-      <c r="I348">
+      <c r="I350">
         <v>670652.7</v>
       </c>
-      <c r="J348">
-        <v>0</v>
-      </c>
-      <c r="K348">
+      <c r="J350">
+        <v>0</v>
+      </c>
+      <c r="K350">
         <v>73076</v>
       </c>
-      <c r="L348" t="s">
-        <v>3</v>
-      </c>
-      <c r="M348" t="s">
-        <v>3</v>
-      </c>
-      <c r="N348" t="s">
-        <v>3</v>
-      </c>
-      <c r="O348">
+      <c r="L350" t="s">
+        <v>3</v>
+      </c>
+      <c r="M350" t="s">
+        <v>3</v>
+      </c>
+      <c r="N350" t="s">
+        <v>3</v>
+      </c>
+      <c r="O350">
         <v>15586.4</v>
       </c>
-      <c r="P348">
-        <v>0</v>
-      </c>
-      <c r="Q348">
-        <v>0</v>
-      </c>
-      <c r="R348">
+      <c r="P350">
+        <v>0</v>
+      </c>
+      <c r="Q350">
+        <v>0</v>
+      </c>
+      <c r="R350">
         <v>20</v>
       </c>
     </row>
-    <row r="349" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A349" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B349" s="3" t="s">
+    <row r="351" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A351" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B351" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C349" t="s">
+      <c r="C351" t="s">
         <v>5</v>
       </c>
-      <c r="D349" t="s">
+      <c r="D351" t="s">
         <v>63</v>
       </c>
-      <c r="E349" t="s">
+      <c r="E351" t="s">
         <v>64</v>
       </c>
-      <c r="F349" t="s">
+      <c r="F351" t="s">
         <v>81</v>
       </c>
-      <c r="G349" t="s">
+      <c r="G351" t="s">
         <v>82</v>
       </c>
-      <c r="H349" t="s">
+      <c r="H351" t="s">
         <v>83</v>
       </c>
-      <c r="I349" t="s">
+      <c r="I351" t="s">
         <v>84</v>
       </c>
-      <c r="J349" t="s">
+      <c r="J351" t="s">
         <v>85</v>
       </c>
-      <c r="K349" t="s">
+      <c r="K351" t="s">
         <v>86</v>
       </c>
-      <c r="L349" t="s">
+      <c r="L351" t="s">
         <v>87</v>
       </c>
-      <c r="M349" t="s">
+      <c r="M351" t="s">
         <v>74</v>
       </c>
-      <c r="N349" t="s">
+      <c r="N351" t="s">
         <v>75</v>
       </c>
-      <c r="O349" t="s">
+      <c r="O351" t="s">
         <v>76</v>
       </c>
-      <c r="P349" t="s">
+      <c r="P351" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A350" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B350" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C350" t="s">
-        <v>98</v>
-      </c>
-      <c r="D350" t="s">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A352" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C352" t="s">
+        <v>101</v>
+      </c>
+      <c r="D352" t="s">
         <v>89</v>
       </c>
-      <c r="E350" t="s">
-        <v>99</v>
-      </c>
-      <c r="F350" t="s">
+      <c r="E352" t="s">
+        <v>102</v>
+      </c>
+      <c r="F352" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A352" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B352" s="3" t="s">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B354" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C352" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="353" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A353" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B353" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C353" t="s">
-        <v>5</v>
-      </c>
-      <c r="D353" t="s">
-        <v>63</v>
-      </c>
-      <c r="E353" t="s">
-        <v>64</v>
-      </c>
-      <c r="F353" t="s">
-        <v>65</v>
-      </c>
-      <c r="G353" t="s">
-        <v>66</v>
-      </c>
-      <c r="H353" t="s">
-        <v>67</v>
-      </c>
-      <c r="I353" t="s">
-        <v>68</v>
-      </c>
-      <c r="J353" t="s">
-        <v>69</v>
-      </c>
-      <c r="K353" t="s">
-        <v>70</v>
-      </c>
-      <c r="L353" t="s">
-        <v>71</v>
-      </c>
-      <c r="M353" t="s">
-        <v>72</v>
-      </c>
-      <c r="N353" t="s">
-        <v>73</v>
-      </c>
-      <c r="O353" t="s">
-        <v>74</v>
-      </c>
-      <c r="P353" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q353" t="s">
-        <v>76</v>
-      </c>
-      <c r="R353" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="354" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A354" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B354" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="C354" t="s">
-        <v>101</v>
-      </c>
-      <c r="D354" t="s">
-        <v>37</v>
-      </c>
-      <c r="E354" t="s">
-        <v>3</v>
-      </c>
-      <c r="F354">
-        <v>-982980</v>
-      </c>
-      <c r="G354">
-        <v>-13216</v>
-      </c>
-      <c r="H354">
-        <v>73926</v>
-      </c>
-      <c r="I354">
-        <v>-982980</v>
-      </c>
-      <c r="J354">
-        <v>13216</v>
-      </c>
-      <c r="K354">
-        <v>73926</v>
-      </c>
-      <c r="L354" t="s">
-        <v>3</v>
-      </c>
-      <c r="M354" t="s">
-        <v>3</v>
-      </c>
-      <c r="N354" t="s">
-        <v>3</v>
-      </c>
-      <c r="O354">
-        <v>15586.4</v>
-      </c>
-      <c r="P354">
-        <v>0</v>
-      </c>
-      <c r="Q354">
-        <v>0</v>
-      </c>
-      <c r="R354">
-        <v>21</v>
+        <v>103</v>
       </c>
     </row>
     <row r="355" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B355" s="2" t="s">
-        <v>79</v>
+      <c r="B355" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C355" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="D355" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E355" t="s">
-        <v>3</v>
-      </c>
-      <c r="F355">
-        <v>-624840</v>
-      </c>
-      <c r="G355">
-        <v>-13216</v>
-      </c>
-      <c r="H355">
-        <v>73926</v>
-      </c>
-      <c r="I355">
-        <v>-624840</v>
-      </c>
-      <c r="J355">
-        <v>13216</v>
-      </c>
-      <c r="K355">
-        <v>73926</v>
+        <v>64</v>
+      </c>
+      <c r="F355" t="s">
+        <v>65</v>
+      </c>
+      <c r="G355" t="s">
+        <v>66</v>
+      </c>
+      <c r="H355" t="s">
+        <v>67</v>
+      </c>
+      <c r="I355" t="s">
+        <v>68</v>
+      </c>
+      <c r="J355" t="s">
+        <v>69</v>
+      </c>
+      <c r="K355" t="s">
+        <v>70</v>
       </c>
       <c r="L355" t="s">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="M355" t="s">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="N355" t="s">
-        <v>3</v>
-      </c>
-      <c r="O355">
-        <v>15240</v>
-      </c>
-      <c r="P355">
-        <v>0</v>
-      </c>
-      <c r="Q355">
-        <v>0</v>
-      </c>
-      <c r="R355">
-        <v>82</v>
+        <v>73</v>
+      </c>
+      <c r="O355" t="s">
+        <v>74</v>
+      </c>
+      <c r="P355" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q355" t="s">
+        <v>76</v>
+      </c>
+      <c r="R355" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="356" spans="1:18" x14ac:dyDescent="0.25">
@@ -15763,7 +15778,7 @@
         <v>79</v>
       </c>
       <c r="C356" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D356" t="s">
         <v>37</v>
@@ -15772,7 +15787,7 @@
         <v>3</v>
       </c>
       <c r="F356">
-        <v>655666.4</v>
+        <v>-982980</v>
       </c>
       <c r="G356">
         <v>-13216</v>
@@ -15781,7 +15796,7 @@
         <v>73926</v>
       </c>
       <c r="I356">
-        <v>655666.4</v>
+        <v>-982980</v>
       </c>
       <c r="J356">
         <v>13216</v>
@@ -15811,6 +15826,62 @@
         <v>21</v>
       </c>
     </row>
+    <row r="357" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A357" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C357" t="s">
+        <v>104</v>
+      </c>
+      <c r="D357" t="s">
+        <v>37</v>
+      </c>
+      <c r="E357" t="s">
+        <v>3</v>
+      </c>
+      <c r="F357">
+        <v>-624840</v>
+      </c>
+      <c r="G357">
+        <v>-13216</v>
+      </c>
+      <c r="H357">
+        <v>73926</v>
+      </c>
+      <c r="I357">
+        <v>-624840</v>
+      </c>
+      <c r="J357">
+        <v>13216</v>
+      </c>
+      <c r="K357">
+        <v>73926</v>
+      </c>
+      <c r="L357" t="s">
+        <v>3</v>
+      </c>
+      <c r="M357" t="s">
+        <v>3</v>
+      </c>
+      <c r="N357" t="s">
+        <v>3</v>
+      </c>
+      <c r="O357">
+        <v>15240</v>
+      </c>
+      <c r="P357">
+        <v>0</v>
+      </c>
+      <c r="Q357">
+        <v>0</v>
+      </c>
+      <c r="R357">
+        <v>82</v>
+      </c>
+    </row>
     <row r="358" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>3</v>
@@ -15819,37 +15890,37 @@
         <v>79</v>
       </c>
       <c r="C358" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D358" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E358" t="s">
         <v>3</v>
       </c>
       <c r="F358">
-        <v>-982980</v>
+        <v>655666.4</v>
       </c>
       <c r="G358">
-        <v>0</v>
+        <v>-13216</v>
       </c>
       <c r="H358">
-        <v>74326</v>
+        <v>73926</v>
       </c>
       <c r="I358">
-        <v>-967393.6</v>
+        <v>655666.4</v>
       </c>
       <c r="J358">
-        <v>0</v>
+        <v>13216</v>
       </c>
       <c r="K358">
-        <v>74326</v>
-      </c>
-      <c r="L358">
-        <v>350</v>
-      </c>
-      <c r="M358">
-        <v>350</v>
+        <v>73926</v>
+      </c>
+      <c r="L358" t="s">
+        <v>3</v>
+      </c>
+      <c r="M358" t="s">
+        <v>3</v>
       </c>
       <c r="N358" t="s">
         <v>3</v>
@@ -15867,62 +15938,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="359" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A359" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B359" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C359" t="s">
-        <v>101</v>
-      </c>
-      <c r="D359" t="s">
-        <v>38</v>
-      </c>
-      <c r="E359" t="s">
-        <v>3</v>
-      </c>
-      <c r="F359">
-        <v>-640080</v>
-      </c>
-      <c r="G359">
-        <v>0</v>
-      </c>
-      <c r="H359">
-        <v>74326</v>
-      </c>
-      <c r="I359">
-        <v>-624840</v>
-      </c>
-      <c r="J359">
-        <v>0</v>
-      </c>
-      <c r="K359">
-        <v>74326</v>
-      </c>
-      <c r="L359">
-        <v>350</v>
-      </c>
-      <c r="M359">
-        <v>350</v>
-      </c>
-      <c r="N359" t="s">
-        <v>3</v>
-      </c>
-      <c r="O359">
-        <v>15240</v>
-      </c>
-      <c r="P359">
-        <v>0</v>
-      </c>
-      <c r="Q359">
-        <v>0</v>
-      </c>
-      <c r="R359">
-        <v>83</v>
-      </c>
-    </row>
     <row r="360" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>3</v>
@@ -15931,7 +15946,7 @@
         <v>79</v>
       </c>
       <c r="C360" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D360" t="s">
         <v>38</v>
@@ -15940,7 +15955,7 @@
         <v>3</v>
       </c>
       <c r="F360">
-        <v>640080</v>
+        <v>-982980</v>
       </c>
       <c r="G360">
         <v>0</v>
@@ -15949,7 +15964,7 @@
         <v>74326</v>
       </c>
       <c r="I360">
-        <v>655666.4</v>
+        <v>-967393.6</v>
       </c>
       <c r="J360">
         <v>0</v>
@@ -15987,7 +16002,7 @@
         <v>79</v>
       </c>
       <c r="C361" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D361" t="s">
         <v>38</v>
@@ -15996,19 +16011,19 @@
         <v>3</v>
       </c>
       <c r="F361">
-        <v>-982980</v>
+        <v>-640080</v>
       </c>
       <c r="G361">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="H361">
         <v>74326</v>
       </c>
       <c r="I361">
-        <v>-967393.6</v>
+        <v>-624840</v>
       </c>
       <c r="J361">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="K361">
         <v>74326</v>
@@ -16023,7 +16038,7 @@
         <v>3</v>
       </c>
       <c r="O361">
-        <v>15586.4</v>
+        <v>15240</v>
       </c>
       <c r="P361">
         <v>0</v>
@@ -16032,7 +16047,7 @@
         <v>0</v>
       </c>
       <c r="R361">
-        <v>21</v>
+        <v>83</v>
       </c>
     </row>
     <row r="362" spans="1:18" x14ac:dyDescent="0.25">
@@ -16043,7 +16058,7 @@
         <v>79</v>
       </c>
       <c r="C362" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D362" t="s">
         <v>38</v>
@@ -16052,19 +16067,19 @@
         <v>3</v>
       </c>
       <c r="F362">
-        <v>-640080</v>
+        <v>640080</v>
       </c>
       <c r="G362">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="H362">
         <v>74326</v>
       </c>
       <c r="I362">
-        <v>-624840</v>
+        <v>655666.4</v>
       </c>
       <c r="J362">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="K362">
         <v>74326</v>
@@ -16079,7 +16094,7 @@
         <v>3</v>
       </c>
       <c r="O362">
-        <v>15240</v>
+        <v>15586.4</v>
       </c>
       <c r="P362">
         <v>0</v>
@@ -16088,7 +16103,7 @@
         <v>0</v>
       </c>
       <c r="R362">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="363" spans="1:18" x14ac:dyDescent="0.25">
@@ -16099,7 +16114,7 @@
         <v>79</v>
       </c>
       <c r="C363" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D363" t="s">
         <v>38</v>
@@ -16108,7 +16123,7 @@
         <v>3</v>
       </c>
       <c r="F363">
-        <v>640080</v>
+        <v>-982980</v>
       </c>
       <c r="G363">
         <v>-6000</v>
@@ -16117,7 +16132,7 @@
         <v>74326</v>
       </c>
       <c r="I363">
-        <v>655666.4</v>
+        <v>-967393.6</v>
       </c>
       <c r="J363">
         <v>-6000</v>
@@ -16155,7 +16170,7 @@
         <v>79</v>
       </c>
       <c r="C364" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D364" t="s">
         <v>38</v>
@@ -16164,19 +16179,19 @@
         <v>3</v>
       </c>
       <c r="F364">
-        <v>-982980</v>
+        <v>-640080</v>
       </c>
       <c r="G364">
-        <v>6000</v>
+        <v>-6000</v>
       </c>
       <c r="H364">
         <v>74326</v>
       </c>
       <c r="I364">
-        <v>-967393.6</v>
+        <v>-624840</v>
       </c>
       <c r="J364">
-        <v>6000</v>
+        <v>-6000</v>
       </c>
       <c r="K364">
         <v>74326</v>
@@ -16191,7 +16206,7 @@
         <v>3</v>
       </c>
       <c r="O364">
-        <v>15586.4</v>
+        <v>15240</v>
       </c>
       <c r="P364">
         <v>0</v>
@@ -16200,7 +16215,7 @@
         <v>0</v>
       </c>
       <c r="R364">
-        <v>21</v>
+        <v>83</v>
       </c>
     </row>
     <row r="365" spans="1:18" x14ac:dyDescent="0.25">
@@ -16211,7 +16226,7 @@
         <v>79</v>
       </c>
       <c r="C365" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D365" t="s">
         <v>38</v>
@@ -16220,19 +16235,19 @@
         <v>3</v>
       </c>
       <c r="F365">
-        <v>-640080</v>
+        <v>640080</v>
       </c>
       <c r="G365">
-        <v>6000</v>
+        <v>-6000</v>
       </c>
       <c r="H365">
         <v>74326</v>
       </c>
       <c r="I365">
-        <v>-624840</v>
+        <v>655666.4</v>
       </c>
       <c r="J365">
-        <v>6000</v>
+        <v>-6000</v>
       </c>
       <c r="K365">
         <v>74326</v>
@@ -16247,7 +16262,7 @@
         <v>3</v>
       </c>
       <c r="O365">
-        <v>15240</v>
+        <v>15586.4</v>
       </c>
       <c r="P365">
         <v>0</v>
@@ -16256,7 +16271,7 @@
         <v>0</v>
       </c>
       <c r="R365">
-        <v>83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="366" spans="1:18" x14ac:dyDescent="0.25">
@@ -16267,7 +16282,7 @@
         <v>79</v>
       </c>
       <c r="C366" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D366" t="s">
         <v>38</v>
@@ -16276,7 +16291,7 @@
         <v>3</v>
       </c>
       <c r="F366">
-        <v>640080</v>
+        <v>-982980</v>
       </c>
       <c r="G366">
         <v>6000</v>
@@ -16285,7 +16300,7 @@
         <v>74326</v>
       </c>
       <c r="I366">
-        <v>655666.4</v>
+        <v>-967393.6</v>
       </c>
       <c r="J366">
         <v>6000</v>
@@ -16315,142 +16330,166 @@
         <v>21</v>
       </c>
     </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A367" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C367" t="s">
+        <v>104</v>
+      </c>
+      <c r="D367" t="s">
+        <v>38</v>
+      </c>
+      <c r="E367" t="s">
+        <v>3</v>
+      </c>
+      <c r="F367">
+        <v>-640080</v>
+      </c>
+      <c r="G367">
+        <v>6000</v>
+      </c>
+      <c r="H367">
+        <v>74326</v>
+      </c>
+      <c r="I367">
+        <v>-624840</v>
+      </c>
+      <c r="J367">
+        <v>6000</v>
+      </c>
+      <c r="K367">
+        <v>74326</v>
+      </c>
+      <c r="L367">
+        <v>350</v>
+      </c>
+      <c r="M367">
+        <v>350</v>
+      </c>
+      <c r="N367" t="s">
+        <v>3</v>
+      </c>
+      <c r="O367">
+        <v>15240</v>
+      </c>
+      <c r="P367">
+        <v>0</v>
+      </c>
+      <c r="Q367">
+        <v>0</v>
+      </c>
+      <c r="R367">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="368" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B368" s="3" t="s">
+      <c r="B368" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C368" t="s">
+        <v>104</v>
+      </c>
+      <c r="D368" t="s">
+        <v>38</v>
+      </c>
+      <c r="E368" t="s">
+        <v>3</v>
+      </c>
+      <c r="F368">
+        <v>640080</v>
+      </c>
+      <c r="G368">
+        <v>6000</v>
+      </c>
+      <c r="H368">
+        <v>74326</v>
+      </c>
+      <c r="I368">
+        <v>655666.4</v>
+      </c>
+      <c r="J368">
+        <v>6000</v>
+      </c>
+      <c r="K368">
+        <v>74326</v>
+      </c>
+      <c r="L368">
+        <v>350</v>
+      </c>
+      <c r="M368">
+        <v>350</v>
+      </c>
+      <c r="N368" t="s">
+        <v>3</v>
+      </c>
+      <c r="O368">
+        <v>15586.4</v>
+      </c>
+      <c r="P368">
+        <v>0</v>
+      </c>
+      <c r="Q368">
+        <v>0</v>
+      </c>
+      <c r="R368">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="370" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A370" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B370" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C368" t="s">
+      <c r="C370" t="s">
         <v>5</v>
       </c>
-      <c r="D368" t="s">
+      <c r="D370" t="s">
         <v>63</v>
       </c>
-      <c r="E368" t="s">
+      <c r="E370" t="s">
         <v>64</v>
       </c>
-      <c r="F368" t="s">
+      <c r="F370" t="s">
         <v>81</v>
       </c>
-      <c r="G368" t="s">
+      <c r="G370" t="s">
         <v>82</v>
       </c>
-      <c r="H368" t="s">
+      <c r="H370" t="s">
         <v>83</v>
       </c>
-      <c r="I368" t="s">
+      <c r="I370" t="s">
         <v>84</v>
       </c>
-      <c r="J368" t="s">
+      <c r="J370" t="s">
         <v>85</v>
       </c>
-      <c r="K368" t="s">
+      <c r="K370" t="s">
         <v>86</v>
       </c>
-      <c r="L368" t="s">
+      <c r="L370" t="s">
         <v>87</v>
       </c>
-      <c r="M368" t="s">
+      <c r="M370" t="s">
         <v>74</v>
       </c>
-      <c r="N368" t="s">
+      <c r="N370" t="s">
         <v>75</v>
       </c>
-      <c r="O368" t="s">
+      <c r="O370" t="s">
         <v>76</v>
       </c>
-      <c r="P368" t="s">
+      <c r="P370" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A369" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B369" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C369" t="s">
-        <v>101</v>
-      </c>
-      <c r="D369" t="s">
-        <v>56</v>
-      </c>
-      <c r="E369" t="s">
-        <v>22</v>
-      </c>
-      <c r="F369">
-        <v>-975186.8</v>
-      </c>
-      <c r="G369">
-        <v>0</v>
-      </c>
-      <c r="H369">
-        <v>74691</v>
-      </c>
-      <c r="I369" t="s">
-        <v>88</v>
-      </c>
-      <c r="J369" t="s">
-        <v>3</v>
-      </c>
-      <c r="K369" t="s">
-        <v>3</v>
-      </c>
-      <c r="L369" t="s">
-        <v>3</v>
-      </c>
-      <c r="M369">
-        <v>15586.4</v>
-      </c>
-      <c r="N369">
-        <v>0</v>
-      </c>
-      <c r="O369">
-        <v>0</v>
-      </c>
-      <c r="P369">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A370" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B370" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C370" t="s">
-        <v>101</v>
-      </c>
-      <c r="D370" t="s">
-        <v>59</v>
-      </c>
-      <c r="E370" t="s">
-        <v>22</v>
-      </c>
-      <c r="F370">
-        <v>-647873.2</v>
-      </c>
-      <c r="G370">
-        <v>0</v>
-      </c>
-      <c r="H370">
-        <v>74691</v>
-      </c>
-      <c r="I370" t="s">
-        <v>88</v>
-      </c>
-      <c r="J370" t="s">
-        <v>3</v>
-      </c>
-      <c r="K370" t="s">
-        <v>3</v>
-      </c>
-      <c r="L370" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="371" spans="1:16" x14ac:dyDescent="0.25">
@@ -16461,16 +16500,16 @@
         <v>79</v>
       </c>
       <c r="C371" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D371" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E371" t="s">
         <v>22</v>
       </c>
       <c r="F371">
-        <v>-617220</v>
+        <v>-975186.8</v>
       </c>
       <c r="G371">
         <v>0</v>
@@ -16491,7 +16530,7 @@
         <v>3</v>
       </c>
       <c r="M371">
-        <v>15240</v>
+        <v>15586.4</v>
       </c>
       <c r="N371">
         <v>0</v>
@@ -16500,7 +16539,7 @@
         <v>0</v>
       </c>
       <c r="P371">
-        <v>81</v>
+        <v>20</v>
       </c>
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.25">
@@ -16511,16 +16550,16 @@
         <v>79</v>
       </c>
       <c r="C372" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D372" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E372" t="s">
         <v>22</v>
       </c>
       <c r="F372">
-        <v>-632460</v>
+        <v>-647873.2</v>
       </c>
       <c r="G372">
         <v>0</v>
@@ -16541,7 +16580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>3</v>
       </c>
@@ -16549,16 +16588,16 @@
         <v>79</v>
       </c>
       <c r="C373" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D373" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E373" t="s">
         <v>22</v>
       </c>
       <c r="F373">
-        <v>632460</v>
+        <v>-617220</v>
       </c>
       <c r="G373">
         <v>0</v>
@@ -16578,8 +16617,20 @@
       <c r="L373" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="374" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M373">
+        <v>15240</v>
+      </c>
+      <c r="N373">
+        <v>0</v>
+      </c>
+      <c r="O373">
+        <v>0</v>
+      </c>
+      <c r="P373">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>3</v>
       </c>
@@ -16587,16 +16638,16 @@
         <v>79</v>
       </c>
       <c r="C374" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D374" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E374" t="s">
         <v>22</v>
       </c>
       <c r="F374">
-        <v>663459.5</v>
+        <v>-632460</v>
       </c>
       <c r="G374">
         <v>0</v>
@@ -16616,18 +16667,6 @@
       <c r="L374" t="s">
         <v>3</v>
       </c>
-      <c r="M374">
-        <v>15586.4</v>
-      </c>
-      <c r="N374">
-        <v>0</v>
-      </c>
-      <c r="O374">
-        <v>0</v>
-      </c>
-      <c r="P374">
-        <v>20</v>
-      </c>
     </row>
     <row r="375" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
@@ -16637,16 +16676,16 @@
         <v>79</v>
       </c>
       <c r="C375" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D375" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E375" t="s">
         <v>22</v>
       </c>
       <c r="F375">
-        <v>647873.2</v>
+        <v>632460</v>
       </c>
       <c r="G375">
         <v>0</v>
@@ -16667,7 +16706,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>3</v>
       </c>
@@ -16675,79 +16714,130 @@
         <v>79</v>
       </c>
       <c r="C376" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D376" t="s">
+        <v>56</v>
+      </c>
+      <c r="E376" t="s">
+        <v>22</v>
+      </c>
+      <c r="F376">
+        <v>663459.5</v>
+      </c>
+      <c r="G376">
+        <v>0</v>
+      </c>
+      <c r="H376">
+        <v>74691</v>
+      </c>
+      <c r="I376" t="s">
+        <v>88</v>
+      </c>
+      <c r="J376" t="s">
+        <v>3</v>
+      </c>
+      <c r="K376" t="s">
+        <v>3</v>
+      </c>
+      <c r="L376" t="s">
+        <v>3</v>
+      </c>
+      <c r="M376">
+        <v>15586.4</v>
+      </c>
+      <c r="N376">
+        <v>0</v>
+      </c>
+      <c r="O376">
+        <v>0</v>
+      </c>
+      <c r="P376">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A377" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C377" t="s">
+        <v>104</v>
+      </c>
+      <c r="D377" t="s">
+        <v>59</v>
+      </c>
+      <c r="E377" t="s">
+        <v>22</v>
+      </c>
+      <c r="F377">
+        <v>647873.2</v>
+      </c>
+      <c r="G377">
+        <v>0</v>
+      </c>
+      <c r="H377">
+        <v>74691</v>
+      </c>
+      <c r="I377" t="s">
+        <v>88</v>
+      </c>
+      <c r="J377" t="s">
+        <v>3</v>
+      </c>
+      <c r="K377" t="s">
+        <v>3</v>
+      </c>
+      <c r="L377" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A378" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C378" t="s">
+        <v>104</v>
+      </c>
+      <c r="D378" t="s">
         <v>89</v>
       </c>
-      <c r="E376" t="s">
-        <v>102</v>
-      </c>
-      <c r="F376" t="s">
+      <c r="E378" t="s">
+        <v>105</v>
+      </c>
+      <c r="F378" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A378" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B378" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C378" t="s">
-        <v>5</v>
-      </c>
-      <c r="D378" t="s">
-        <v>105</v>
-      </c>
-      <c r="E378" t="s">
-        <v>106</v>
-      </c>
-      <c r="F378" t="s">
-        <v>107</v>
-      </c>
-      <c r="G378" t="s">
-        <v>108</v>
-      </c>
-      <c r="H378" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A379" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B379" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C379" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B380" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B380" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C380" t="s">
+        <v>108</v>
+      </c>
+      <c r="D380" t="s">
+        <v>109</v>
+      </c>
+      <c r="E380" t="s">
+        <v>110</v>
+      </c>
+      <c r="F380" t="s">
         <v>111</v>
       </c>
-      <c r="C380" t="s">
+      <c r="G380" t="s">
         <v>112</v>
       </c>
-      <c r="D380" t="s">
-        <v>80</v>
-      </c>
-      <c r="E380" t="s">
+      <c r="H380" t="s">
         <v>113</v>
-      </c>
-      <c r="F380">
-        <v>-640080</v>
-      </c>
-      <c r="G380">
-        <v>-13716</v>
-      </c>
-      <c r="H380">
-        <v>0</v>
       </c>
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.25">
@@ -16755,274 +16845,504 @@
         <v>3</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C381" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="D381" t="s">
+        <v>115</v>
+      </c>
+      <c r="E381" t="s">
+        <v>3</v>
+      </c>
+      <c r="F381" t="s">
+        <v>3</v>
+      </c>
+      <c r="G381">
+        <v>500</v>
+      </c>
+      <c r="H381" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A382" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C382" t="s">
         <v>80</v>
       </c>
-      <c r="E381" t="s">
-        <v>113</v>
-      </c>
-      <c r="F381">
-        <v>640080</v>
-      </c>
-      <c r="G381">
-        <v>-13716</v>
-      </c>
-      <c r="H381">
-        <v>0</v>
+      <c r="D382" t="s">
+        <v>117</v>
+      </c>
+      <c r="E382" t="s">
+        <v>3</v>
+      </c>
+      <c r="F382" t="s">
+        <v>3</v>
+      </c>
+      <c r="G382">
+        <v>500</v>
+      </c>
+      <c r="H382" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B383" s="3" t="s">
-        <v>104</v>
+      <c r="B383" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="C383" t="s">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="D383" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="E383" t="s">
-        <v>106</v>
+        <v>3</v>
       </c>
       <c r="F383" t="s">
-        <v>107</v>
-      </c>
-      <c r="G383" t="s">
-        <v>108</v>
+        <v>3</v>
+      </c>
+      <c r="G383">
+        <v>5000</v>
       </c>
       <c r="H383" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A384" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B384" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C384" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B385" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
+      </c>
+      <c r="B385" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="C385" t="s">
-        <v>115</v>
+        <v>5</v>
       </c>
       <c r="D385" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="E385" t="s">
-        <v>113</v>
-      </c>
-      <c r="F385">
-        <v>-1155660.8</v>
-      </c>
-      <c r="G385">
+        <v>123</v>
+      </c>
+      <c r="F385" t="s">
+        <v>124</v>
+      </c>
+      <c r="G385" t="s">
+        <v>125</v>
+      </c>
+      <c r="H385" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A386" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B386" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C386" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A387" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B387" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C387" t="s">
+        <v>129</v>
+      </c>
+      <c r="D387" t="s">
+        <v>80</v>
+      </c>
+      <c r="E387" t="s">
+        <v>130</v>
+      </c>
+      <c r="F387">
+        <v>-640080</v>
+      </c>
+      <c r="G387">
         <v>-13716</v>
       </c>
-      <c r="H385">
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A386" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B386" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C386" t="s">
-        <v>115</v>
-      </c>
-      <c r="D386" t="s">
-        <v>93</v>
-      </c>
-      <c r="E386" t="s">
-        <v>113</v>
-      </c>
-      <c r="F386">
-        <v>-1155660.8</v>
-      </c>
-      <c r="G386">
-        <v>13716</v>
-      </c>
-      <c r="H386">
-        <v>45000</v>
+      <c r="H387">
+        <v>0</v>
       </c>
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B388" s="3" t="s">
-        <v>104</v>
+      <c r="B388" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="C388" t="s">
-        <v>5</v>
+        <v>129</v>
       </c>
       <c r="D388" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="E388" t="s">
-        <v>106</v>
-      </c>
-      <c r="F388" t="s">
-        <v>107</v>
-      </c>
-      <c r="G388" t="s">
-        <v>108</v>
-      </c>
-      <c r="H388" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A389" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B389" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C389" t="s">
-        <v>116</v>
+        <v>130</v>
+      </c>
+      <c r="F388">
+        <v>640080</v>
+      </c>
+      <c r="G388">
+        <v>-13716</v>
+      </c>
+      <c r="H388">
+        <v>0</v>
       </c>
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B390" s="2" t="s">
-        <v>111</v>
+      <c r="B390" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="C390" t="s">
-        <v>117</v>
+        <v>5</v>
       </c>
       <c r="D390" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="E390" t="s">
-        <v>113</v>
-      </c>
-      <c r="F390">
-        <v>-982980</v>
-      </c>
-      <c r="G390">
+        <v>123</v>
+      </c>
+      <c r="F390" t="s">
+        <v>124</v>
+      </c>
+      <c r="G390" t="s">
+        <v>125</v>
+      </c>
+      <c r="H390" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A391" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B391" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C391" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A392" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B392" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C392" t="s">
+        <v>132</v>
+      </c>
+      <c r="D392" t="s">
+        <v>93</v>
+      </c>
+      <c r="E392" t="s">
+        <v>130</v>
+      </c>
+      <c r="F392">
+        <v>-1155660.8</v>
+      </c>
+      <c r="G392">
         <v>-13716</v>
       </c>
-      <c r="H390">
-        <v>74076</v>
-      </c>
-    </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A391" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B391" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C391" t="s">
-        <v>117</v>
-      </c>
-      <c r="D391" t="s">
-        <v>98</v>
-      </c>
-      <c r="E391" t="s">
-        <v>113</v>
-      </c>
-      <c r="F391">
-        <v>-982980</v>
-      </c>
-      <c r="G391">
-        <v>13716</v>
-      </c>
-      <c r="H391">
-        <v>74076</v>
+      <c r="H392">
+        <v>45000</v>
       </c>
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B393" s="3" t="s">
-        <v>104</v>
+      <c r="B393" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="C393" t="s">
-        <v>5</v>
+        <v>132</v>
       </c>
       <c r="D393" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E393" t="s">
-        <v>106</v>
-      </c>
-      <c r="F393" t="s">
-        <v>107</v>
-      </c>
-      <c r="G393" t="s">
-        <v>108</v>
-      </c>
-      <c r="H393" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A394" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B394" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C394" t="s">
-        <v>118</v>
+        <v>130</v>
+      </c>
+      <c r="F393">
+        <v>-1155660.8</v>
+      </c>
+      <c r="G393">
+        <v>13716</v>
+      </c>
+      <c r="H393">
+        <v>45000</v>
       </c>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B395" s="2" t="s">
-        <v>111</v>
+      <c r="B395" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="C395" t="s">
-        <v>119</v>
+        <v>5</v>
       </c>
       <c r="D395" t="s">
+        <v>122</v>
+      </c>
+      <c r="E395" t="s">
+        <v>123</v>
+      </c>
+      <c r="F395" t="s">
+        <v>124</v>
+      </c>
+      <c r="G395" t="s">
+        <v>125</v>
+      </c>
+      <c r="H395" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A396" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B396" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C396" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A397" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B397" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C397" t="s">
+        <v>134</v>
+      </c>
+      <c r="D397" t="s">
+        <v>96</v>
+      </c>
+      <c r="E397" t="s">
+        <v>130</v>
+      </c>
+      <c r="F397">
+        <v>-982980</v>
+      </c>
+      <c r="G397">
+        <v>-13716</v>
+      </c>
+      <c r="H397">
+        <v>92000</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A398" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B398" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C398" t="s">
+        <v>134</v>
+      </c>
+      <c r="D398" t="s">
+        <v>96</v>
+      </c>
+      <c r="E398" t="s">
+        <v>130</v>
+      </c>
+      <c r="F398">
+        <v>-982980</v>
+      </c>
+      <c r="G398">
+        <v>13716</v>
+      </c>
+      <c r="H398">
+        <v>92000</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A400" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B400" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C400" t="s">
+        <v>5</v>
+      </c>
+      <c r="D400" t="s">
+        <v>122</v>
+      </c>
+      <c r="E400" t="s">
+        <v>123</v>
+      </c>
+      <c r="F400" t="s">
+        <v>124</v>
+      </c>
+      <c r="G400" t="s">
+        <v>125</v>
+      </c>
+      <c r="H400" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A401" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B401" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C401" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A402" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B402" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C402" t="s">
+        <v>136</v>
+      </c>
+      <c r="D402" t="s">
         <v>101</v>
       </c>
-      <c r="E395" t="s">
-        <v>113</v>
-      </c>
-      <c r="F395">
+      <c r="E402" t="s">
+        <v>130</v>
+      </c>
+      <c r="F402">
         <v>-982980</v>
       </c>
-      <c r="G395">
+      <c r="G402">
+        <v>-13716</v>
+      </c>
+      <c r="H402">
+        <v>74076</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A403" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B403" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C403" t="s">
+        <v>136</v>
+      </c>
+      <c r="D403" t="s">
+        <v>101</v>
+      </c>
+      <c r="E403" t="s">
+        <v>130</v>
+      </c>
+      <c r="F403">
+        <v>-982980</v>
+      </c>
+      <c r="G403">
+        <v>13716</v>
+      </c>
+      <c r="H403">
+        <v>74076</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A405" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B405" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C405" t="s">
+        <v>5</v>
+      </c>
+      <c r="D405" t="s">
+        <v>122</v>
+      </c>
+      <c r="E405" t="s">
+        <v>123</v>
+      </c>
+      <c r="F405" t="s">
+        <v>124</v>
+      </c>
+      <c r="G405" t="s">
+        <v>125</v>
+      </c>
+      <c r="H405" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A406" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B406" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C406" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A407" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B407" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C407" t="s">
+        <v>138</v>
+      </c>
+      <c r="D407" t="s">
+        <v>104</v>
+      </c>
+      <c r="E407" t="s">
+        <v>130</v>
+      </c>
+      <c r="F407">
+        <v>-982980</v>
+      </c>
+      <c r="G407">
         <v>-13216</v>
       </c>
-      <c r="H395">
+      <c r="H407">
         <v>73926</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A396" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B396" s="2" t="s">
-        <v>120</v>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A408" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B408" s="2" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/plate3d/PLATE3D_GGB.xlsx
+++ b/plate3d/PLATE3D_GGB.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2652" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2687" uniqueCount="146">
   <si>
     <t>GOLDEN GATE BRIDGE  ·  1280.16 m main span  ·  mm, Z up</t>
   </si>
@@ -331,7 +331,7 @@
     <t>sc.fb_1</t>
   </si>
   <si>
-    <t>three drawings, named by the sheet. Save DXF asks for the scale</t>
+    <t>eight drawings, named by the sheet - and the scale is the sheet's too</t>
   </si>
   <si>
     <t># VIEW</t>
@@ -370,7 +370,28 @@
     <t>TOWER - ELEVATION ALONG THE BRIDGE</t>
   </si>
   <si>
-    <t>STIFFENING TRUSS - GENERAL ARRANGEMENT</t>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>TOWER - PLAN</t>
+  </si>
+  <si>
+    <t>MAIN CABLE - ANCHORAGE TO ANCHORAGE</t>
+  </si>
+  <si>
+    <t>HANGER ROPES - ELEVATION</t>
+  </si>
+  <si>
+    <t>STIFFENING TRUSS - ELEVATION</t>
+  </si>
+  <si>
+    <t>as.trs</t>
+  </si>
+  <si>
+    <t>STIFFENING TRUSSES - PLAN</t>
+  </si>
+  <si>
+    <t>FLOOR SYSTEM AND DECK - PLAN</t>
   </si>
   <si>
     <t>one assembly per part - towers, main cables, ropes, trusses, deck</t>
@@ -419,9 +440,6 @@
   </si>
   <si>
     <t>STIFFENING TRUSSES - one plane, both sides</t>
-  </si>
-  <si>
-    <t>as.trs</t>
   </si>
   <si>
     <t>FLOOR SYSTEM AND DECK</t>
@@ -824,7 +842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R408"/>
+  <dimension ref="A1:R413"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
@@ -16900,59 +16918,100 @@
         <v>114</v>
       </c>
       <c r="C383" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="D383" t="s">
+        <v>119</v>
+      </c>
+      <c r="E383" t="s">
+        <v>3</v>
+      </c>
+      <c r="F383" t="s">
+        <v>3</v>
+      </c>
+      <c r="G383">
+        <v>500</v>
+      </c>
+      <c r="H383" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A384" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B384" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C384" t="s">
+        <v>93</v>
+      </c>
+      <c r="D384" t="s">
         <v>117</v>
       </c>
-      <c r="E383" t="s">
-        <v>3</v>
-      </c>
-      <c r="F383" t="s">
-        <v>3</v>
-      </c>
-      <c r="G383">
+      <c r="E384" t="s">
+        <v>3</v>
+      </c>
+      <c r="F384" t="s">
+        <v>3</v>
+      </c>
+      <c r="G384">
         <v>5000</v>
       </c>
-      <c r="H383" t="s">
-        <v>119</v>
+      <c r="H384" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B385" s="3" t="s">
-        <v>121</v>
+        <v>3</v>
+      </c>
+      <c r="B385" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="C385" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
       <c r="D385" t="s">
+        <v>117</v>
+      </c>
+      <c r="E385" t="s">
+        <v>3</v>
+      </c>
+      <c r="F385" t="s">
+        <v>3</v>
+      </c>
+      <c r="G385">
+        <v>5000</v>
+      </c>
+      <c r="H385" t="s">
         <v>122</v>
       </c>
-      <c r="E385" t="s">
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A386" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C386" t="s">
+        <v>101</v>
+      </c>
+      <c r="D386" t="s">
+        <v>117</v>
+      </c>
+      <c r="E386" t="s">
+        <v>3</v>
+      </c>
+      <c r="F386" t="s">
+        <v>3</v>
+      </c>
+      <c r="G386">
+        <v>5000</v>
+      </c>
+      <c r="H386" t="s">
         <v>123</v>
-      </c>
-      <c r="F385" t="s">
-        <v>124</v>
-      </c>
-      <c r="G385" t="s">
-        <v>125</v>
-      </c>
-      <c r="H385" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A386" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B386" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C386" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.25">
@@ -16960,25 +17019,25 @@
         <v>3</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C387" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D387" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="E387" t="s">
-        <v>130</v>
-      </c>
-      <c r="F387">
-        <v>-640080</v>
+        <v>3</v>
+      </c>
+      <c r="F387" t="s">
+        <v>3</v>
       </c>
       <c r="G387">
-        <v>-13716</v>
-      </c>
-      <c r="H387">
-        <v>0</v>
+        <v>5000</v>
+      </c>
+      <c r="H387" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.25">
@@ -16986,51 +17045,51 @@
         <v>3</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C388" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="D388" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="E388" t="s">
-        <v>130</v>
-      </c>
-      <c r="F388">
-        <v>640080</v>
+        <v>3</v>
+      </c>
+      <c r="F388" t="s">
+        <v>3</v>
       </c>
       <c r="G388">
-        <v>-13716</v>
-      </c>
-      <c r="H388">
-        <v>0</v>
+        <v>5000</v>
+      </c>
+      <c r="H388" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
-        <v>3</v>
+        <v>127</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C390" t="s">
         <v>5</v>
       </c>
       <c r="D390" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E390" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F390" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G390" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H390" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -17041,7 +17100,7 @@
         <v>60</v>
       </c>
       <c r="C391" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.25">
@@ -17049,25 +17108,25 @@
         <v>3</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C392" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D392" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E392" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F392">
-        <v>-1155660.8</v>
+        <v>-640080</v>
       </c>
       <c r="G392">
         <v>-13716</v>
       </c>
       <c r="H392">
-        <v>45000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.25">
@@ -17075,25 +17134,25 @@
         <v>3</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C393" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D393" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="E393" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F393">
-        <v>-1155660.8</v>
+        <v>640080</v>
       </c>
       <c r="G393">
-        <v>13716</v>
+        <v>-13716</v>
       </c>
       <c r="H393">
-        <v>45000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.25">
@@ -17101,25 +17160,25 @@
         <v>3</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C395" t="s">
         <v>5</v>
       </c>
       <c r="D395" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E395" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F395" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G395" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H395" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
@@ -17130,7 +17189,7 @@
         <v>60</v>
       </c>
       <c r="C396" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.25">
@@ -17138,25 +17197,25 @@
         <v>3</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C397" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D397" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E397" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F397">
-        <v>-982980</v>
+        <v>-1155660.8</v>
       </c>
       <c r="G397">
         <v>-13716</v>
       </c>
       <c r="H397">
-        <v>92000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.25">
@@ -17164,25 +17223,25 @@
         <v>3</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C398" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D398" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E398" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F398">
-        <v>-982980</v>
+        <v>-1155660.8</v>
       </c>
       <c r="G398">
         <v>13716</v>
       </c>
       <c r="H398">
-        <v>92000</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.25">
@@ -17190,25 +17249,25 @@
         <v>3</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C400" t="s">
         <v>5</v>
       </c>
       <c r="D400" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E400" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F400" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G400" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H400" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
@@ -17219,7 +17278,7 @@
         <v>60</v>
       </c>
       <c r="C401" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.25">
@@ -17227,16 +17286,16 @@
         <v>3</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C402" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D402" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E402" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F402">
         <v>-982980</v>
@@ -17245,7 +17304,7 @@
         <v>-13716</v>
       </c>
       <c r="H402">
-        <v>74076</v>
+        <v>92000</v>
       </c>
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.25">
@@ -17253,16 +17312,16 @@
         <v>3</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C403" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D403" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E403" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F403">
         <v>-982980</v>
@@ -17271,7 +17330,7 @@
         <v>13716</v>
       </c>
       <c r="H403">
-        <v>74076</v>
+        <v>92000</v>
       </c>
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.25">
@@ -17279,25 +17338,25 @@
         <v>3</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C405" t="s">
         <v>5</v>
       </c>
       <c r="D405" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E405" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F405" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G405" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H405" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
@@ -17308,7 +17367,7 @@
         <v>60</v>
       </c>
       <c r="C406" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.25">
@@ -17316,33 +17375,122 @@
         <v>3</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C407" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="D407" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E407" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F407">
         <v>-982980</v>
       </c>
       <c r="G407">
+        <v>-13716</v>
+      </c>
+      <c r="H407">
+        <v>74076</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A408" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B408" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C408" t="s">
+        <v>124</v>
+      </c>
+      <c r="D408" t="s">
+        <v>101</v>
+      </c>
+      <c r="E408" t="s">
+        <v>137</v>
+      </c>
+      <c r="F408">
+        <v>-982980</v>
+      </c>
+      <c r="G408">
+        <v>13716</v>
+      </c>
+      <c r="H408">
+        <v>74076</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A410" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B410" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C410" t="s">
+        <v>5</v>
+      </c>
+      <c r="D410" t="s">
+        <v>129</v>
+      </c>
+      <c r="E410" t="s">
+        <v>130</v>
+      </c>
+      <c r="F410" t="s">
+        <v>131</v>
+      </c>
+      <c r="G410" t="s">
+        <v>132</v>
+      </c>
+      <c r="H410" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A411" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B411" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C411" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A412" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B412" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C412" t="s">
+        <v>144</v>
+      </c>
+      <c r="D412" t="s">
+        <v>104</v>
+      </c>
+      <c r="E412" t="s">
+        <v>137</v>
+      </c>
+      <c r="F412">
+        <v>-982980</v>
+      </c>
+      <c r="G412">
         <v>-13216</v>
       </c>
-      <c r="H407">
+      <c r="H412">
         <v>73926</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A408" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B408" s="2" t="s">
-        <v>139</v>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A413" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B413" s="2" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/plate3d/PLATE3D_GGB.xlsx
+++ b/plate3d/PLATE3D_GGB.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2687" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2694" uniqueCount="148">
   <si>
     <t>GOLDEN GATE BRIDGE  ·  1280.16 m main span  ·  mm, Z up</t>
   </si>
@@ -331,7 +331,7 @@
     <t>sc.fb_1</t>
   </si>
   <si>
-    <t>eight drawings, named by the sheet - and the scale is the sheet's too</t>
+    <t>nine drawings. The first is ALL - the whole bridge on one sheet</t>
   </si>
   <si>
     <t># VIEW</t>
@@ -358,13 +358,19 @@
     <t>VIEW</t>
   </si>
   <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>FRONT</t>
+  </si>
+  <si>
+    <t>GOLDEN GATE BRIDGE - GENERAL ARRANGEMENT</t>
+  </si>
+  <si>
     <t>RIGHT</t>
   </si>
   <si>
     <t>TOWER - ELEVATION ACROSS THE BRIDGE</t>
-  </si>
-  <si>
-    <t>FRONT</t>
   </si>
   <si>
     <t>TOWER - ELEVATION ALONG THE BRIDGE</t>
@@ -842,7 +848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R413"/>
+  <dimension ref="A1:R414"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
@@ -16866,10 +16872,10 @@
         <v>114</v>
       </c>
       <c r="C381" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="D381" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E381" t="s">
         <v>3</v>
@@ -16878,10 +16884,10 @@
         <v>3</v>
       </c>
       <c r="G381">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="H381" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.25">
@@ -16895,7 +16901,7 @@
         <v>80</v>
       </c>
       <c r="D382" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E382" t="s">
         <v>3</v>
@@ -16907,7 +16913,7 @@
         <v>500</v>
       </c>
       <c r="H382" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.25">
@@ -16921,7 +16927,7 @@
         <v>80</v>
       </c>
       <c r="D383" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E383" t="s">
         <v>3</v>
@@ -16944,10 +16950,10 @@
         <v>114</v>
       </c>
       <c r="C384" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D384" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E384" t="s">
         <v>3</v>
@@ -16956,10 +16962,10 @@
         <v>3</v>
       </c>
       <c r="G384">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="H384" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.25">
@@ -16970,10 +16976,10 @@
         <v>114</v>
       </c>
       <c r="C385" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D385" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E385" t="s">
         <v>3</v>
@@ -16985,7 +16991,7 @@
         <v>5000</v>
       </c>
       <c r="H385" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.25">
@@ -16996,10 +17002,10 @@
         <v>114</v>
       </c>
       <c r="C386" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D386" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E386" t="s">
         <v>3</v>
@@ -17011,7 +17017,7 @@
         <v>5000</v>
       </c>
       <c r="H386" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.25">
@@ -17022,10 +17028,10 @@
         <v>114</v>
       </c>
       <c r="C387" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="D387" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E387" t="s">
         <v>3</v>
@@ -17048,10 +17054,10 @@
         <v>114</v>
       </c>
       <c r="C388" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="D388" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E388" t="s">
         <v>3</v>
@@ -17063,90 +17069,90 @@
         <v>5000</v>
       </c>
       <c r="H388" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A390" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B390" s="3" t="s">
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A389" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C389" t="s">
+        <v>104</v>
+      </c>
+      <c r="D389" t="s">
+        <v>121</v>
+      </c>
+      <c r="E389" t="s">
+        <v>3</v>
+      </c>
+      <c r="F389" t="s">
+        <v>3</v>
+      </c>
+      <c r="G389">
+        <v>5000</v>
+      </c>
+      <c r="H389" t="s">
         <v>128</v>
       </c>
-      <c r="C390" t="s">
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A391" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B391" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C391" t="s">
         <v>5</v>
       </c>
-      <c r="D390" t="s">
-        <v>129</v>
-      </c>
-      <c r="E390" t="s">
-        <v>130</v>
-      </c>
-      <c r="F390" t="s">
+      <c r="D391" t="s">
         <v>131</v>
       </c>
-      <c r="G390" t="s">
+      <c r="E391" t="s">
         <v>132</v>
       </c>
-      <c r="H390" t="s">
+      <c r="F391" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A391" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B391" s="3" t="s">
+      <c r="G391" t="s">
+        <v>134</v>
+      </c>
+      <c r="H391" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A392" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B392" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="C391" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A392" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B392" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="C392" t="s">
         <v>136</v>
       </c>
-      <c r="D392" t="s">
-        <v>80</v>
-      </c>
-      <c r="E392" t="s">
-        <v>137</v>
-      </c>
-      <c r="F392">
-        <v>-640080</v>
-      </c>
-      <c r="G392">
-        <v>-13716</v>
-      </c>
-      <c r="H392">
-        <v>0</v>
-      </c>
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C393" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D393" t="s">
         <v>80</v>
       </c>
       <c r="E393" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F393">
-        <v>640080</v>
+        <v>-640080</v>
       </c>
       <c r="G393">
         <v>-13716</v>
@@ -17155,67 +17161,67 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A395" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B395" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C395" t="s">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A394" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B394" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C394" t="s">
+        <v>138</v>
+      </c>
+      <c r="D394" t="s">
+        <v>80</v>
+      </c>
+      <c r="E394" t="s">
+        <v>139</v>
+      </c>
+      <c r="F394">
+        <v>640080</v>
+      </c>
+      <c r="G394">
+        <v>-13716</v>
+      </c>
+      <c r="H394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A396" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B396" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C396" t="s">
         <v>5</v>
       </c>
-      <c r="D395" t="s">
-        <v>129</v>
-      </c>
-      <c r="E395" t="s">
-        <v>130</v>
-      </c>
-      <c r="F395" t="s">
+      <c r="D396" t="s">
         <v>131</v>
       </c>
-      <c r="G395" t="s">
+      <c r="E396" t="s">
         <v>132</v>
       </c>
-      <c r="H395" t="s">
+      <c r="F396" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A396" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B396" s="3" t="s">
+      <c r="G396" t="s">
+        <v>134</v>
+      </c>
+      <c r="H396" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A397" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B397" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C396" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A397" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B397" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="C397" t="s">
-        <v>139</v>
-      </c>
-      <c r="D397" t="s">
-        <v>93</v>
-      </c>
-      <c r="E397" t="s">
-        <v>137</v>
-      </c>
-      <c r="F397">
-        <v>-1155660.8</v>
-      </c>
-      <c r="G397">
-        <v>-13716</v>
-      </c>
-      <c r="H397">
-        <v>45000</v>
+        <v>140</v>
       </c>
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.25">
@@ -17223,88 +17229,88 @@
         <v>3</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C398" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D398" t="s">
         <v>93</v>
       </c>
       <c r="E398" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F398">
         <v>-1155660.8</v>
       </c>
       <c r="G398">
-        <v>13716</v>
+        <v>-13716</v>
       </c>
       <c r="H398">
         <v>45000</v>
       </c>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A400" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B400" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C400" t="s">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A399" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B399" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C399" t="s">
+        <v>141</v>
+      </c>
+      <c r="D399" t="s">
+        <v>93</v>
+      </c>
+      <c r="E399" t="s">
+        <v>139</v>
+      </c>
+      <c r="F399">
+        <v>-1155660.8</v>
+      </c>
+      <c r="G399">
+        <v>13716</v>
+      </c>
+      <c r="H399">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A401" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B401" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C401" t="s">
         <v>5</v>
       </c>
-      <c r="D400" t="s">
-        <v>129</v>
-      </c>
-      <c r="E400" t="s">
-        <v>130</v>
-      </c>
-      <c r="F400" t="s">
+      <c r="D401" t="s">
         <v>131</v>
       </c>
-      <c r="G400" t="s">
+      <c r="E401" t="s">
         <v>132</v>
       </c>
-      <c r="H400" t="s">
+      <c r="F401" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A401" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B401" s="3" t="s">
+      <c r="G401" t="s">
+        <v>134</v>
+      </c>
+      <c r="H401" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A402" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B402" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C401" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A402" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B402" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="C402" t="s">
-        <v>141</v>
-      </c>
-      <c r="D402" t="s">
-        <v>96</v>
-      </c>
-      <c r="E402" t="s">
-        <v>137</v>
-      </c>
-      <c r="F402">
-        <v>-982980</v>
-      </c>
-      <c r="G402">
-        <v>-13716</v>
-      </c>
-      <c r="H402">
-        <v>92000</v>
+        <v>142</v>
       </c>
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.25">
@@ -17312,88 +17318,88 @@
         <v>3</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C403" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D403" t="s">
         <v>96</v>
       </c>
       <c r="E403" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F403">
         <v>-982980</v>
       </c>
       <c r="G403">
-        <v>13716</v>
+        <v>-13716</v>
       </c>
       <c r="H403">
         <v>92000</v>
       </c>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A405" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B405" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C405" t="s">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A404" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B404" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C404" t="s">
+        <v>143</v>
+      </c>
+      <c r="D404" t="s">
+        <v>96</v>
+      </c>
+      <c r="E404" t="s">
+        <v>139</v>
+      </c>
+      <c r="F404">
+        <v>-982980</v>
+      </c>
+      <c r="G404">
+        <v>13716</v>
+      </c>
+      <c r="H404">
+        <v>92000</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A406" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B406" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C406" t="s">
         <v>5</v>
       </c>
-      <c r="D405" t="s">
-        <v>129</v>
-      </c>
-      <c r="E405" t="s">
-        <v>130</v>
-      </c>
-      <c r="F405" t="s">
+      <c r="D406" t="s">
         <v>131</v>
       </c>
-      <c r="G405" t="s">
+      <c r="E406" t="s">
         <v>132</v>
       </c>
-      <c r="H405" t="s">
+      <c r="F406" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A406" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B406" s="3" t="s">
+      <c r="G406" t="s">
+        <v>134</v>
+      </c>
+      <c r="H406" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A407" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B407" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C406" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A407" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B407" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="C407" t="s">
-        <v>124</v>
-      </c>
-      <c r="D407" t="s">
-        <v>101</v>
-      </c>
-      <c r="E407" t="s">
-        <v>137</v>
-      </c>
-      <c r="F407">
-        <v>-982980</v>
-      </c>
-      <c r="G407">
-        <v>-13716</v>
-      </c>
-      <c r="H407">
-        <v>74076</v>
+        <v>144</v>
       </c>
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.25">
@@ -17401,96 +17407,122 @@
         <v>3</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C408" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D408" t="s">
         <v>101</v>
       </c>
       <c r="E408" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F408">
         <v>-982980</v>
       </c>
       <c r="G408">
-        <v>13716</v>
+        <v>-13716</v>
       </c>
       <c r="H408">
         <v>74076</v>
       </c>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A410" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B410" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C410" t="s">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A409" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B409" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C409" t="s">
+        <v>126</v>
+      </c>
+      <c r="D409" t="s">
+        <v>101</v>
+      </c>
+      <c r="E409" t="s">
+        <v>139</v>
+      </c>
+      <c r="F409">
+        <v>-982980</v>
+      </c>
+      <c r="G409">
+        <v>13716</v>
+      </c>
+      <c r="H409">
+        <v>74076</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A411" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B411" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C411" t="s">
         <v>5</v>
       </c>
-      <c r="D410" t="s">
-        <v>129</v>
-      </c>
-      <c r="E410" t="s">
-        <v>130</v>
-      </c>
-      <c r="F410" t="s">
+      <c r="D411" t="s">
         <v>131</v>
       </c>
-      <c r="G410" t="s">
+      <c r="E411" t="s">
         <v>132</v>
       </c>
-      <c r="H410" t="s">
+      <c r="F411" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A411" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B411" s="3" t="s">
+      <c r="G411" t="s">
+        <v>134</v>
+      </c>
+      <c r="H411" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A412" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B412" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C411" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A412" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B412" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="C412" t="s">
-        <v>144</v>
-      </c>
-      <c r="D412" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A413" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B413" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C413" t="s">
+        <v>146</v>
+      </c>
+      <c r="D413" t="s">
         <v>104</v>
       </c>
-      <c r="E412" t="s">
-        <v>137</v>
-      </c>
-      <c r="F412">
+      <c r="E413" t="s">
+        <v>139</v>
+      </c>
+      <c r="F413">
         <v>-982980</v>
       </c>
-      <c r="G412">
+      <c r="G413">
         <v>-13216</v>
       </c>
-      <c r="H412">
+      <c r="H413">
         <v>73926</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A413" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B413" s="2" t="s">
-        <v>145</v>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A414" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B414" s="2" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
